--- a/2.RASGOS/Rasgos_unificado_todas_las_bases.xlsx
+++ b/2.RASGOS/Rasgos_unificado_todas_las_bases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ314"/>
+  <dimension ref="A1:AJ312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>590</v>
+      </c>
       <c r="G2" t="n">
         <v>8633</v>
       </c>
@@ -701,7 +703,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -795,7 +801,11 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -885,7 +895,11 @@
           <t>mas 10 Nutrientes</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -916,7 +930,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>580</v>
+      </c>
       <c r="G5" t="n">
         <v>8641</v>
       </c>
@@ -979,7 +995,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1010,7 +1030,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>579</v>
+      </c>
       <c r="G6" t="n">
         <v>8642</v>
       </c>
@@ -1073,7 +1095,11 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1104,7 +1130,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>611</v>
+      </c>
       <c r="G7" t="n">
         <v>8643</v>
       </c>
@@ -1159,7 +1187,11 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1190,7 +1222,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>606</v>
+      </c>
       <c r="G8" t="n">
         <v>8644</v>
       </c>
@@ -1253,7 +1287,11 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1284,7 +1322,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>600</v>
+      </c>
       <c r="G9" t="n">
         <v>8649</v>
       </c>
@@ -1349,7 +1389,7 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stem_water_content_pct fuera de rango [30-250]; </t>
+          <t xml:space="preserve">stem_water_content_pct fuera de rango [30-250]; old_ID asignado por taxonomía en el plot (verificar); </t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1382,7 +1422,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>598</v>
+      </c>
       <c r="G10" t="n">
         <v>8651</v>
       </c>
@@ -1445,7 +1487,11 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1539,7 +1585,11 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1570,7 +1620,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>592</v>
+      </c>
       <c r="G12" t="n">
         <v>8656</v>
       </c>
@@ -1627,7 +1679,11 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1658,7 +1714,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>1417</v>
+      </c>
       <c r="G13" t="n">
         <v>8658</v>
       </c>
@@ -1721,7 +1779,11 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1807,7 +1869,11 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1838,7 +1904,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>1414</v>
+      </c>
       <c r="G15" t="n">
         <v>8664</v>
       </c>
@@ -1901,7 +1969,11 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -1932,7 +2004,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>1411</v>
+      </c>
       <c r="G16" t="n">
         <v>8665</v>
       </c>
@@ -1995,7 +2069,11 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2026,7 +2104,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>1406</v>
+      </c>
       <c r="G17" t="n">
         <v>8666</v>
       </c>
@@ -2085,7 +2165,11 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2116,7 +2200,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>1407</v>
+      </c>
       <c r="G18" t="n">
         <v>8667</v>
       </c>
@@ -2175,7 +2261,11 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2206,7 +2296,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>1404</v>
+      </c>
       <c r="G19" t="n">
         <v>8669</v>
       </c>
@@ -2269,7 +2361,11 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2300,7 +2396,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1400</v>
+      </c>
       <c r="G20" t="n">
         <v>8672</v>
       </c>
@@ -2363,7 +2461,11 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2394,7 +2496,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>1398</v>
+      </c>
       <c r="G21" t="n">
         <v>8678</v>
       </c>
@@ -2457,7 +2561,11 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2488,7 +2596,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>1389</v>
+      </c>
       <c r="G22" t="n">
         <v>8685</v>
       </c>
@@ -2551,7 +2661,11 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -2582,7 +2696,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>1390</v>
+      </c>
       <c r="G23" t="n">
         <v>8686</v>
       </c>
@@ -2645,7 +2761,11 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -3011,7 +3131,7 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr">
         <is>
-          <t xml:space="preserve">valor de longitud interpretado como fecha por Excel (dato original a revisar); </t>
+          <t xml:space="preserve">longitud interpretada como fecha por Excel (revisar dato original); </t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3279,7 +3399,11 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -3365,7 +3489,11 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -4124,7 +4252,9 @@
         <v>23</v>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>577</v>
+      </c>
       <c r="G40" t="n">
         <v>8985</v>
       </c>
@@ -4173,7 +4303,11 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old_ID asignado por taxonomía en el plot (verificar); </t>
+        </is>
+      </c>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -4547,7 +4681,7 @@
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr">
         <is>
-          <t xml:space="preserve">n_leaves traia texto mezclado (20 pesadas, 22 escaneads), se tomo el primer numero; new_tree_ID_2025=8721 duplicado en la base secundaria (01); </t>
+          <t xml:space="preserve">n_leaves traía texto (20 pesadas, 22 escaneads), se tomó el primer número; new_ID=8721 repetido en la base 01; </t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -4643,7 +4777,7 @@
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr">
         <is>
-          <t xml:space="preserve">longitud reportada como 2 fragmentos (1.9-2.7), se sumo el largo total; </t>
+          <t xml:space="preserve">longitud en 2 fragmentos (1.9-2.7), se sumó el largo total; </t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -5017,7 +5151,7 @@
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr">
         <is>
-          <t xml:space="preserve">longitud reportada como 2 fragmentos (2.1-2.6), se sumo el largo total; </t>
+          <t xml:space="preserve">longitud en 2 fragmentos (2.1-2.6), se sumó el largo total; </t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -5134,7 +5268,9 @@
         <v>28</v>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>743</v>
+      </c>
       <c r="G51" t="n">
         <v>8713</v>
       </c>
@@ -5197,7 +5333,7 @@
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="inlineStr">
         <is>
-          <t xml:space="preserve">n_leaves no interpretable (pesadas 20 pero escaneadas 18. Peso de 18 = 19,35); </t>
+          <t xml:space="preserve">n_leaves no interpretable (pesadas 20 pero escaneadas 18. Peso de 18 = 19,35); old_ID asignado por taxonomía en el plot (verificar); </t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -5279,7 +5415,11 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ52" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -6095,7 +6235,11 @@
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ61" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -6177,7 +6321,7 @@
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr">
         <is>
-          <t xml:space="preserve">n_leaves traia texto mezclado (20-21 eliminar 1 de escaneados), se tomo el primer numero; </t>
+          <t xml:space="preserve">n_leaves traía texto (20-21 eliminar 1 de escaneados), se tomó el primer número; sin old_ID; </t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -6359,7 +6503,7 @@
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="inlineStr">
         <is>
-          <t xml:space="preserve">n_leaves traia texto mezclado (20 pesadas, escaneadas 17- Peso 17=11,91), se tomo el primer numero; </t>
+          <t xml:space="preserve">n_leaves traía texto (20 pesadas, escaneadas 17- Peso 17=11,91), se tomó el primer número; </t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -6799,7 +6943,7 @@
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="inlineStr">
         <is>
-          <t xml:space="preserve">n_leaves traia texto mezclado (11 escaneadas, 20 pesadas 11h=6,36), se tomo el primer numero; </t>
+          <t xml:space="preserve">n_leaves traía texto (11 escaneadas, 20 pesadas 11h=6,36), se tomó el primer número; </t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -7143,7 +7287,7 @@
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="inlineStr">
         <is>
-          <t xml:space="preserve">n_leaves traia texto mezclado (16. Eliminar 1 escaneado. 17 escaneadas), se tomo el primer numero; leaf_area_cm2 fuera de rango fisico plausible (revisar escaneo original), excluido de SLA; </t>
+          <t xml:space="preserve">n_leaves traía texto (16. Eliminar 1 escaneado. 17 escaneadas), se tomó el primer número; leaf_area_cm2 fuera de rango (revisar escaneo), excluido de SLA; </t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -7673,7 +7817,11 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin old_ID; </t>
+        </is>
+      </c>
       <c r="AJ79" t="inlineStr">
         <is>
           <t>03__Rasgos_Galeras.xlsx (principal)</t>
@@ -7755,7 +7903,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; sin old_ID; </t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -7837,7 +7985,7 @@
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -7919,7 +8067,7 @@
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -8001,7 +8149,7 @@
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; longitud reportada como 3 fragmentos (1.3-1.4-1.5), se sumo el largo total; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; longitud en 3 fragmentos (1.3-1.4-1.5), se sumó el largo total; </t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -8083,7 +8231,7 @@
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -8161,7 +8309,7 @@
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -8243,7 +8391,7 @@
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -8321,7 +8469,7 @@
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -8403,7 +8551,7 @@
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -8481,7 +8629,7 @@
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -8559,7 +8707,7 @@
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -8641,7 +8789,7 @@
       <c r="AH91" t="inlineStr"/>
       <c r="AI91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presente solo en base secundaria (01); posible informacion faltante en 03; </t>
+          <t xml:space="preserve">Solo en base 01; posible información faltante en 03; </t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -24326,7 +24474,9 @@
       <c r="L264" t="n">
         <v>3000</v>
       </c>
-      <c r="M264" t="inlineStr"/>
+      <c r="M264" t="n">
+        <v>20</v>
+      </c>
       <c r="N264" t="n">
         <v>0.6899999999999999</v>
       </c>
@@ -24434,7 +24584,9 @@
       <c r="L265" t="n">
         <v>3000</v>
       </c>
-      <c r="M265" t="inlineStr"/>
+      <c r="M265" t="n">
+        <v>20</v>
+      </c>
       <c r="N265" t="n">
         <v>0.76</v>
       </c>
@@ -24542,7 +24694,9 @@
       <c r="L266" t="n">
         <v>1000</v>
       </c>
-      <c r="M266" t="inlineStr"/>
+      <c r="M266" t="n">
+        <v>20</v>
+      </c>
       <c r="N266" t="n">
         <v>46.05</v>
       </c>
@@ -24650,7 +24804,9 @@
       <c r="L267" t="n">
         <v>1000</v>
       </c>
-      <c r="M267" t="inlineStr"/>
+      <c r="M267" t="n">
+        <v>20</v>
+      </c>
       <c r="N267" t="n">
         <v>35.63</v>
       </c>
@@ -24721,16 +24877,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>CaNu</t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CaNu_5</t>
+          <t>BoN_4</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -24738,80 +24894,82 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>1012</v>
+        <v>2062</v>
       </c>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weinmania </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>loxensis</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="K268" s="2" t="n">
-        <v>45623</v>
+        <v>45617</v>
       </c>
       <c r="L268" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M268" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="M268" t="n">
+        <v>20</v>
+      </c>
       <c r="N268" t="n">
-        <v>1.17</v>
+        <v>34.11</v>
       </c>
       <c r="O268" t="n">
-        <v>0.52</v>
+        <v>18.97</v>
       </c>
       <c r="P268" t="n">
-        <v>31.193</v>
+        <v>1362.462</v>
       </c>
       <c r="Q268" t="n">
-        <v>59.98653846153847</v>
+        <v>71.82192936215077</v>
       </c>
       <c r="R268" t="n">
-        <v>444.4444444444445</v>
+        <v>556.1418938727646</v>
       </c>
       <c r="S268" t="n">
-        <v>0.3273333333333333</v>
+        <v>0.2016666666666667</v>
       </c>
       <c r="T268" t="n">
-        <v>0.536</v>
+        <v>0.788</v>
       </c>
       <c r="U268" t="n">
-        <v>0.536</v>
+        <v>0.788</v>
       </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" t="n">
-        <v>0.9270783265798529</v>
+        <v>0.897369378775291</v>
       </c>
       <c r="X268" t="inlineStr"/>
       <c r="Y268" t="inlineStr"/>
       <c r="Z268" t="n">
-        <v>0.472759833658854</v>
+        <v>0.549719054790026</v>
       </c>
       <c r="AA268" t="n">
-        <v>0.20265699609375</v>
+        <v>0</v>
       </c>
       <c r="AB268" t="n">
-        <v>5.6138734938151</v>
+        <v>1.66626440551181</v>
       </c>
       <c r="AC268" t="n">
-        <v>0.0479679111328125</v>
+        <v>0.0407151466535433</v>
       </c>
       <c r="AD268" t="n">
-        <v>3.52186953613281</v>
+        <v>4.75845919914698</v>
       </c>
       <c r="AE268" t="n">
-        <v>4.03459293391927</v>
+        <v>0.613313642716535</v>
       </c>
       <c r="AF268" t="n">
-        <v>0.260680309570312</v>
+        <v>0.409117678149606</v>
       </c>
       <c r="AG268" t="n">
-        <v>0.610831482421875</v>
+        <v>1.43008032283465</v>
       </c>
       <c r="AH268" t="inlineStr"/>
       <c r="AI268" t="inlineStr"/>
@@ -24846,7 +25004,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
@@ -24866,24 +25024,26 @@
       <c r="L269" t="n">
         <v>3000</v>
       </c>
-      <c r="M269" t="inlineStr"/>
+      <c r="M269" t="n">
+        <v>20</v>
+      </c>
       <c r="N269" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="O269" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="P269" t="n">
-        <v>34.5482815</v>
+        <v>31.193</v>
       </c>
       <c r="Q269" t="n">
-        <v>75.1049597826087</v>
+        <v>59.98653846153847</v>
       </c>
       <c r="R269" t="n">
-        <v>446.6019417475728</v>
+        <v>444.4444444444445</v>
       </c>
       <c r="S269" t="n">
-        <v>0.2506666666666666</v>
+        <v>0.3273333333333333</v>
       </c>
       <c r="T269" t="n">
         <v>0.536</v>
@@ -24893,33 +25053,33 @@
       </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" t="n">
-        <v>0.8116908953746352</v>
+        <v>0.9270783265798529</v>
       </c>
       <c r="X269" t="inlineStr"/>
       <c r="Y269" t="inlineStr"/>
       <c r="Z269" t="n">
-        <v>0.541857143239625</v>
+        <v>0.472759833658854</v>
       </c>
       <c r="AA269" t="n">
-        <v>0.321099295180723</v>
+        <v>0.20265699609375</v>
       </c>
       <c r="AB269" t="n">
-        <v>7.28925633601071</v>
+        <v>5.6138734938151</v>
       </c>
       <c r="AC269" t="n">
-        <v>0.07023062148594381</v>
+        <v>0.0479679111328125</v>
       </c>
       <c r="AD269" t="n">
-        <v>3.52717978514056</v>
+        <v>3.52186953613281</v>
       </c>
       <c r="AE269" t="n">
-        <v>3.9237978206158</v>
+        <v>4.03459293391927</v>
       </c>
       <c r="AF269" t="n">
-        <v>0</v>
+        <v>0.260680309570312</v>
       </c>
       <c r="AG269" t="n">
-        <v>0.697454173694779</v>
+        <v>0.610831482421875</v>
       </c>
       <c r="AH269" t="inlineStr"/>
       <c r="AI269" t="inlineStr"/>
@@ -24954,80 +25114,82 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>19006</v>
+        <v>1014</v>
       </c>
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t xml:space="preserve">Weinmania </t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>loxensis</t>
         </is>
       </c>
       <c r="K270" s="2" t="n">
-        <v>45628</v>
+        <v>45623</v>
       </c>
       <c r="L270" t="n">
         <v>3000</v>
       </c>
-      <c r="M270" t="inlineStr"/>
+      <c r="M270" t="n">
+        <v>20</v>
+      </c>
       <c r="N270" t="n">
-        <v>21.13</v>
+        <v>1.03</v>
       </c>
       <c r="O270" t="n">
-        <v>5.25</v>
+        <v>0.46</v>
       </c>
       <c r="P270" t="n">
-        <v>356.5100514</v>
+        <v>34.5482815</v>
       </c>
       <c r="Q270" t="n">
-        <v>67.90667645714286</v>
+        <v>75.1049597826087</v>
       </c>
       <c r="R270" t="n">
-        <v>248.4619025082821</v>
+        <v>446.6019417475728</v>
       </c>
       <c r="S270" t="n">
-        <v>0.4718333333333334</v>
+        <v>0.2506666666666666</v>
       </c>
       <c r="T270" t="n">
-        <v>0.585</v>
+        <v>0.536</v>
       </c>
       <c r="U270" t="n">
-        <v>0.585</v>
+        <v>0.536</v>
       </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" t="n">
-        <v>0.7721673844560661</v>
+        <v>0.8116908953746352</v>
       </c>
       <c r="X270" t="inlineStr"/>
       <c r="Y270" t="inlineStr"/>
       <c r="Z270" t="n">
-        <v>0.907596492739274</v>
+        <v>0.541857143239625</v>
       </c>
       <c r="AA270" t="n">
-        <v>0.0175934554455446</v>
+        <v>0.321099295180723</v>
       </c>
       <c r="AB270" t="n">
-        <v>9.0347323630363</v>
+        <v>7.28925633601071</v>
       </c>
       <c r="AC270" t="n">
-        <v>0.0875066772277228</v>
+        <v>0.07023062148594381</v>
       </c>
       <c r="AD270" t="n">
-        <v>8.1845332990099</v>
+        <v>3.52717978514056</v>
       </c>
       <c r="AE270" t="n">
-        <v>5.95553381815182</v>
+        <v>3.9237978206158</v>
       </c>
       <c r="AF270" t="n">
-        <v>0.0623804960396038</v>
+        <v>0</v>
       </c>
       <c r="AG270" t="n">
-        <v>1.41709760792079</v>
+        <v>0.697454173694779</v>
       </c>
       <c r="AH270" t="inlineStr"/>
       <c r="AI270" t="inlineStr"/>
@@ -25045,16 +25207,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t>CaNu</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>BoN_8</t>
+          <t>CaNu_5</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -25062,80 +25224,82 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>1925</v>
+        <v>19006</v>
       </c>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="K271" s="2" t="n">
-        <v>45615</v>
+        <v>45628</v>
       </c>
       <c r="L271" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M271" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="M271" t="n">
+        <v>20</v>
+      </c>
       <c r="N271" t="n">
-        <v>23.53</v>
+        <v>21.13</v>
       </c>
       <c r="O271" t="n">
-        <v>12.94</v>
+        <v>5.25</v>
       </c>
       <c r="P271" t="n">
-        <v>971.109</v>
+        <v>356.5100514</v>
       </c>
       <c r="Q271" t="n">
-        <v>75.04706336939722</v>
+        <v>67.90667645714286</v>
       </c>
       <c r="R271" t="n">
-        <v>549.93625159371</v>
+        <v>248.4619025082821</v>
       </c>
       <c r="S271" t="n">
-        <v>0.2181666666666667</v>
+        <v>0.4718333333333334</v>
       </c>
       <c r="T271" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="U271" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" t="n">
-        <v>0.7955101291596506</v>
+        <v>0.7721673844560661</v>
       </c>
       <c r="X271" t="inlineStr"/>
       <c r="Y271" t="inlineStr"/>
       <c r="Z271" t="n">
-        <v>0.631807111000663</v>
+        <v>0.907596492739274</v>
       </c>
       <c r="AA271" t="n">
-        <v>0.0834799317428761</v>
+        <v>0.0175934554455446</v>
       </c>
       <c r="AB271" t="n">
-        <v>2.08940880715706</v>
+        <v>9.0347323630363</v>
       </c>
       <c r="AC271" t="n">
-        <v>0.0261547952286282</v>
+        <v>0.0875066772277228</v>
       </c>
       <c r="AD271" t="n">
-        <v>5.07295081047051</v>
+        <v>8.1845332990099</v>
       </c>
       <c r="AE271" t="n">
-        <v>0.590802970178926</v>
+        <v>5.95553381815182</v>
       </c>
       <c r="AF271" t="n">
-        <v>0</v>
+        <v>0.0623804960396038</v>
       </c>
       <c r="AG271" t="n">
-        <v>1.47536828230616</v>
+        <v>1.41709760792079</v>
       </c>
       <c r="AH271" t="inlineStr"/>
       <c r="AI271" t="inlineStr"/>
@@ -25190,7 +25354,9 @@
       <c r="L272" t="n">
         <v>1000</v>
       </c>
-      <c r="M272" t="inlineStr"/>
+      <c r="M272" t="n">
+        <v>20</v>
+      </c>
       <c r="N272" t="n">
         <v>23.53</v>
       </c>
@@ -25278,7 +25444,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
@@ -25298,24 +25464,26 @@
       <c r="L273" t="n">
         <v>1000</v>
       </c>
-      <c r="M273" t="inlineStr"/>
+      <c r="M273" t="n">
+        <v>20</v>
+      </c>
       <c r="N273" t="n">
-        <v>23.53</v>
+        <v>32.01</v>
       </c>
       <c r="O273" t="n">
-        <v>12.94</v>
+        <v>18.07</v>
       </c>
       <c r="P273" t="n">
-        <v>971.109</v>
+        <v>1374.346</v>
       </c>
       <c r="Q273" t="n">
-        <v>75.04706336939722</v>
+        <v>76.05677919203099</v>
       </c>
       <c r="R273" t="n">
-        <v>549.93625159371</v>
+        <v>564.5110902842863</v>
       </c>
       <c r="S273" t="n">
-        <v>0.2181666666666667</v>
+        <v>0.2113333333333334</v>
       </c>
       <c r="T273" t="n">
         <v>0.788</v>
@@ -25325,33 +25493,33 @@
       </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" t="n">
-        <v>0.7955101291596506</v>
+        <v>0.7360922335505269</v>
       </c>
       <c r="X273" t="inlineStr"/>
       <c r="Y273" t="inlineStr"/>
       <c r="Z273" t="n">
-        <v>0.631807111000663</v>
+        <v>0.519642683828383</v>
       </c>
       <c r="AA273" t="n">
-        <v>0.0834799317428761</v>
+        <v>0.06390046963696371</v>
       </c>
       <c r="AB273" t="n">
-        <v>2.08940880715706</v>
+        <v>3.27365324158416</v>
       </c>
       <c r="AC273" t="n">
-        <v>0.0261547952286282</v>
+        <v>0.0387997594059406</v>
       </c>
       <c r="AD273" t="n">
-        <v>5.07295081047051</v>
+        <v>3.80597948151815</v>
       </c>
       <c r="AE273" t="n">
-        <v>0.590802970178926</v>
+        <v>1.22128953168317</v>
       </c>
       <c r="AF273" t="n">
-        <v>0</v>
+        <v>0.519960008910891</v>
       </c>
       <c r="AG273" t="n">
-        <v>1.47536828230616</v>
+        <v>1.47892905049505</v>
       </c>
       <c r="AH273" t="inlineStr"/>
       <c r="AI273" t="inlineStr"/>
@@ -25386,80 +25554,82 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>1925</v>
+        <v>1930</v>
       </c>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>racemosa</t>
         </is>
       </c>
       <c r="K274" s="2" t="n">
-        <v>45615</v>
+        <v>45618</v>
       </c>
       <c r="L274" t="n">
         <v>1000</v>
       </c>
-      <c r="M274" t="inlineStr"/>
+      <c r="M274" t="n">
+        <v>20</v>
+      </c>
       <c r="N274" t="n">
-        <v>23.53</v>
+        <v>14.88</v>
       </c>
       <c r="O274" t="n">
-        <v>12.94</v>
+        <v>7.29</v>
       </c>
       <c r="P274" t="n">
-        <v>971.109</v>
+        <v>592.412</v>
       </c>
       <c r="Q274" t="n">
-        <v>75.04706336939722</v>
+        <v>81.26364883401921</v>
       </c>
       <c r="R274" t="n">
-        <v>549.93625159371</v>
+        <v>489.9193548387096</v>
       </c>
       <c r="S274" t="n">
-        <v>0.2181666666666667</v>
+        <v>0.2175</v>
       </c>
       <c r="T274" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="U274" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" t="n">
-        <v>0.7955101291596506</v>
+        <v>1.010900000742724</v>
       </c>
       <c r="X274" t="inlineStr"/>
       <c r="Y274" t="inlineStr"/>
       <c r="Z274" t="n">
-        <v>0.631807111000663</v>
+        <v>0.739226720261438</v>
       </c>
       <c r="AA274" t="n">
-        <v>0.0834799317428761</v>
+        <v>0</v>
       </c>
       <c r="AB274" t="n">
-        <v>2.08940880715706</v>
+        <v>23.4330010039216</v>
       </c>
       <c r="AC274" t="n">
-        <v>0.0261547952286282</v>
+        <v>0.0650237794117647</v>
       </c>
       <c r="AD274" t="n">
-        <v>5.07295081047051</v>
+        <v>8.94187097777778</v>
       </c>
       <c r="AE274" t="n">
-        <v>0.590802970178926</v>
+        <v>2.13839180588235</v>
       </c>
       <c r="AF274" t="n">
-        <v>0</v>
+        <v>0.0108368715686276</v>
       </c>
       <c r="AG274" t="n">
-        <v>1.47536828230616</v>
+        <v>1.06759855784314</v>
       </c>
       <c r="AH274" t="inlineStr"/>
       <c r="AI274" t="inlineStr"/>
@@ -25494,7 +25664,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>1927</v>
+        <v>1942</v>
       </c>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
@@ -25514,24 +25684,26 @@
       <c r="L275" t="n">
         <v>1000</v>
       </c>
-      <c r="M275" t="inlineStr"/>
+      <c r="M275" t="n">
+        <v>20</v>
+      </c>
       <c r="N275" t="n">
-        <v>32.01</v>
+        <v>29.39</v>
       </c>
       <c r="O275" t="n">
-        <v>18.07</v>
+        <v>14.21</v>
       </c>
       <c r="P275" t="n">
-        <v>1374.346</v>
+        <v>1379.564</v>
       </c>
       <c r="Q275" t="n">
-        <v>76.05677919203099</v>
+        <v>97.08402533427164</v>
       </c>
       <c r="R275" t="n">
-        <v>564.5110902842863</v>
+        <v>483.4977883633889</v>
       </c>
       <c r="S275" t="n">
-        <v>0.2113333333333334</v>
+        <v>0.1978333333333333</v>
       </c>
       <c r="T275" t="n">
         <v>0.788</v>
@@ -25541,33 +25713,33 @@
       </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" t="n">
-        <v>0.7360922335505269</v>
+        <v>0.735031199700364</v>
       </c>
       <c r="X275" t="inlineStr"/>
       <c r="Y275" t="inlineStr"/>
       <c r="Z275" t="n">
-        <v>0.519642683828383</v>
+        <v>0.891906181936322</v>
       </c>
       <c r="AA275" t="n">
-        <v>0.06390046963696371</v>
+        <v>0.00385622839506174</v>
       </c>
       <c r="AB275" t="n">
-        <v>3.27365324158416</v>
+        <v>1.30120972319688</v>
       </c>
       <c r="AC275" t="n">
-        <v>0.0387997594059406</v>
+        <v>0.0234081588693957</v>
       </c>
       <c r="AD275" t="n">
-        <v>3.80597948151815</v>
+        <v>6.67395967089019</v>
       </c>
       <c r="AE275" t="n">
-        <v>1.22128953168317</v>
+        <v>0.809801712475634</v>
       </c>
       <c r="AF275" t="n">
-        <v>0.519960008910891</v>
+        <v>0</v>
       </c>
       <c r="AG275" t="n">
-        <v>1.47892905049505</v>
+        <v>1.13647001072125</v>
       </c>
       <c r="AH275" t="inlineStr"/>
       <c r="AI275" t="inlineStr"/>
@@ -25602,80 +25774,82 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>1930</v>
+        <v>7546</v>
       </c>
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clarisia </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>racemosa</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="K276" s="2" t="n">
-        <v>45618</v>
+        <v>45615</v>
       </c>
       <c r="L276" t="n">
         <v>1000</v>
       </c>
-      <c r="M276" t="inlineStr"/>
+      <c r="M276" t="n">
+        <v>20</v>
+      </c>
       <c r="N276" t="n">
-        <v>14.88</v>
+        <v>39.5</v>
       </c>
       <c r="O276" t="n">
-        <v>7.29</v>
+        <v>19.58</v>
       </c>
       <c r="P276" t="n">
-        <v>592.412</v>
+        <v>1645.405</v>
       </c>
       <c r="Q276" t="n">
-        <v>81.26364883401921</v>
+        <v>84.03498467824311</v>
       </c>
       <c r="R276" t="n">
-        <v>489.9193548387096</v>
+        <v>495.6962025316456</v>
       </c>
       <c r="S276" t="n">
-        <v>0.2175</v>
+        <v>0.2036666666666667</v>
       </c>
       <c r="T276" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
       <c r="U276" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" t="n">
-        <v>1.010900000742724</v>
+        <v>0.8265453692769162</v>
       </c>
       <c r="X276" t="inlineStr"/>
       <c r="Y276" t="inlineStr"/>
       <c r="Z276" t="n">
-        <v>0.739226720261438</v>
+        <v>0.736298419596354</v>
       </c>
       <c r="AA276" t="n">
+        <v>0.185877903645833</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>2.4404321875</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>0.02788258203125</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>6.11920316634115</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>0.798882657226562</v>
+      </c>
+      <c r="AF276" t="n">
         <v>0</v>
       </c>
-      <c r="AB276" t="n">
-        <v>23.4330010039216</v>
-      </c>
-      <c r="AC276" t="n">
-        <v>0.0650237794117647</v>
-      </c>
-      <c r="AD276" t="n">
-        <v>8.94187097777778</v>
-      </c>
-      <c r="AE276" t="n">
-        <v>2.13839180588235</v>
-      </c>
-      <c r="AF276" t="n">
-        <v>0.0108368715686276</v>
-      </c>
       <c r="AG276" t="n">
-        <v>1.06759855784314</v>
+        <v>1.09328859863281</v>
       </c>
       <c r="AH276" t="inlineStr"/>
       <c r="AI276" t="inlineStr"/>
@@ -25693,16 +25867,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t>CaNu</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BoN_8</t>
+          <t>CaNu_10</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -25710,80 +25884,82 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>1942</v>
+        <v>19011</v>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="K277" s="2" t="n">
-        <v>45615</v>
+        <v>45629</v>
       </c>
       <c r="L277" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M277" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="M277" t="n">
+        <v>20</v>
+      </c>
       <c r="N277" t="n">
-        <v>29.39</v>
+        <v>21.61</v>
       </c>
       <c r="O277" t="n">
-        <v>14.21</v>
+        <v>7.56</v>
       </c>
       <c r="P277" t="n">
-        <v>1379.564</v>
+        <v>363.3769189</v>
       </c>
       <c r="Q277" t="n">
-        <v>97.08402533427164</v>
+        <v>48.06573001322752</v>
       </c>
       <c r="R277" t="n">
-        <v>483.4977883633889</v>
+        <v>349.8380379453956</v>
       </c>
       <c r="S277" t="n">
-        <v>0.1978333333333333</v>
+        <v>0.4893333333333334</v>
       </c>
       <c r="T277" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="U277" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="V277" t="inlineStr"/>
       <c r="W277" t="n">
-        <v>0.735031199700364</v>
+        <v>0.8063857261238205</v>
       </c>
       <c r="X277" t="inlineStr"/>
       <c r="Y277" t="inlineStr"/>
       <c r="Z277" t="n">
-        <v>0.891906181936322</v>
+        <v>0.737201217191601</v>
       </c>
       <c r="AA277" t="n">
-        <v>0.00385622839506174</v>
+        <v>0.008867909448818901</v>
       </c>
       <c r="AB277" t="n">
-        <v>1.30120972319688</v>
+        <v>6.68384700459318</v>
       </c>
       <c r="AC277" t="n">
-        <v>0.0234081588693957</v>
+        <v>0.055109875984252</v>
       </c>
       <c r="AD277" t="n">
-        <v>6.67395967089019</v>
+        <v>8.151757136811019</v>
       </c>
       <c r="AE277" t="n">
-        <v>0.809801712475634</v>
+        <v>4.9055342355643</v>
       </c>
       <c r="AF277" t="n">
-        <v>0</v>
+        <v>0.40571225492126</v>
       </c>
       <c r="AG277" t="n">
-        <v>1.13647001072125</v>
+        <v>1.05768773326772</v>
       </c>
       <c r="AH277" t="inlineStr"/>
       <c r="AI277" t="inlineStr"/>
@@ -25801,16 +25977,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t>CaNu</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>BoN_8</t>
+          <t>CaNu_10</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -25818,80 +25994,82 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>7546</v>
+        <v>5819</v>
       </c>
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Weinmania </t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>loxensis</t>
         </is>
       </c>
       <c r="K278" s="2" t="n">
-        <v>45615</v>
+        <v>45629</v>
       </c>
       <c r="L278" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M278" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="M278" t="n">
+        <v>20</v>
+      </c>
       <c r="N278" t="n">
-        <v>39.5</v>
+        <v>0.99</v>
       </c>
       <c r="O278" t="n">
-        <v>19.58</v>
+        <v>0.43</v>
       </c>
       <c r="P278" t="n">
-        <v>1645.405</v>
+        <v>30.4448543</v>
       </c>
       <c r="Q278" t="n">
-        <v>84.03498467824311</v>
+        <v>70.80198674418605</v>
       </c>
       <c r="R278" t="n">
-        <v>495.6962025316456</v>
+        <v>434.3434343434344</v>
       </c>
       <c r="S278" t="n">
-        <v>0.2036666666666667</v>
+        <v>0.2598333333333333</v>
       </c>
       <c r="T278" t="n">
-        <v>0.788</v>
+        <v>0.536</v>
       </c>
       <c r="U278" t="n">
-        <v>0.788</v>
+        <v>0.536</v>
       </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" t="n">
-        <v>0.8265453692769162</v>
+        <v>0.791265993758999</v>
       </c>
       <c r="X278" t="inlineStr"/>
       <c r="Y278" t="inlineStr"/>
       <c r="Z278" t="n">
-        <v>0.736298419596354</v>
+        <v>0.608936419471947</v>
       </c>
       <c r="AA278" t="n">
-        <v>0.185877903645833</v>
+        <v>0.496632411881188</v>
       </c>
       <c r="AB278" t="n">
-        <v>2.4404321875</v>
+        <v>5.5283124679868</v>
       </c>
       <c r="AC278" t="n">
-        <v>0.02788258203125</v>
+        <v>0.06487703465346541</v>
       </c>
       <c r="AD278" t="n">
-        <v>6.11920316634115</v>
+        <v>2.68533988514851</v>
       </c>
       <c r="AE278" t="n">
-        <v>0.798882657226562</v>
+        <v>6.10167327953795</v>
       </c>
       <c r="AF278" t="n">
         <v>0</v>
       </c>
       <c r="AG278" t="n">
-        <v>1.09328859863281</v>
+        <v>0.810691586138614</v>
       </c>
       <c r="AH278" t="inlineStr"/>
       <c r="AI278" t="inlineStr"/>
@@ -25914,11 +26092,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CaNu_10</t>
+          <t>CaNu_1</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -25926,7 +26104,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>19011</v>
+        <v>19003</v>
       </c>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
@@ -25941,29 +26119,31 @@
         </is>
       </c>
       <c r="K279" s="2" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="L279" t="n">
         <v>3000</v>
       </c>
-      <c r="M279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>20</v>
+      </c>
       <c r="N279" t="n">
-        <v>21.61</v>
+        <v>18.77</v>
       </c>
       <c r="O279" t="n">
-        <v>7.56</v>
+        <v>4.32</v>
       </c>
       <c r="P279" t="n">
-        <v>363.3769189</v>
+        <v>404.1618411</v>
       </c>
       <c r="Q279" t="n">
-        <v>48.06573001322752</v>
+        <v>93.55598173611111</v>
       </c>
       <c r="R279" t="n">
-        <v>349.8380379453956</v>
+        <v>230.1545018646777</v>
       </c>
       <c r="S279" t="n">
-        <v>0.4893333333333334</v>
+        <v>0.4125000000000001</v>
       </c>
       <c r="T279" t="n">
         <v>0.585</v>
@@ -25973,33 +26153,33 @@
       </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" t="n">
-        <v>0.8063857261238205</v>
+        <v>0.7050569934332617</v>
       </c>
       <c r="X279" t="inlineStr"/>
       <c r="Y279" t="inlineStr"/>
       <c r="Z279" t="n">
-        <v>0.737201217191601</v>
+        <v>0.905815394205729</v>
       </c>
       <c r="AA279" t="n">
-        <v>0.008867909448818901</v>
+        <v>0.0122335712890625</v>
       </c>
       <c r="AB279" t="n">
-        <v>6.68384700459318</v>
+        <v>6.43516091178385</v>
       </c>
       <c r="AC279" t="n">
-        <v>0.055109875984252</v>
+        <v>0.0610385927734375</v>
       </c>
       <c r="AD279" t="n">
-        <v>8.151757136811019</v>
+        <v>6.62207567382812</v>
       </c>
       <c r="AE279" t="n">
-        <v>4.9055342355643</v>
+        <v>8.93958169368489</v>
       </c>
       <c r="AF279" t="n">
-        <v>0.40571225492126</v>
+        <v>0.06749272167968751</v>
       </c>
       <c r="AG279" t="n">
-        <v>1.05768773326772</v>
+        <v>1.70840612597656</v>
       </c>
       <c r="AH279" t="inlineStr"/>
       <c r="AI279" t="inlineStr"/>
@@ -26017,16 +26197,16 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CaNu</t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>CaNu_10</t>
+          <t>BoN_12</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -26034,80 +26214,82 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>5819</v>
+        <v>2176</v>
       </c>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weinmania </t>
+          <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>loxensis</t>
+          <t>racemosa</t>
         </is>
       </c>
       <c r="K280" s="2" t="n">
-        <v>45629</v>
+        <v>45649</v>
       </c>
       <c r="L280" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M280" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="M280" t="n">
+        <v>20</v>
+      </c>
       <c r="N280" t="n">
-        <v>0.99</v>
+        <v>15.52</v>
       </c>
       <c r="O280" t="n">
-        <v>0.43</v>
+        <v>6.82</v>
       </c>
       <c r="P280" t="n">
-        <v>30.4448543</v>
+        <v>701.997</v>
       </c>
       <c r="Q280" t="n">
-        <v>70.80198674418605</v>
+        <v>102.9321114369501</v>
       </c>
       <c r="R280" t="n">
-        <v>434.3434343434344</v>
+        <v>439.4329896907217</v>
       </c>
       <c r="S280" t="n">
-        <v>0.2598333333333333</v>
+        <v>0.1893333333333334</v>
       </c>
       <c r="T280" t="n">
-        <v>0.536</v>
+        <v>0.585</v>
       </c>
       <c r="U280" t="n">
-        <v>0.536</v>
+        <v>0.585</v>
       </c>
       <c r="V280" t="inlineStr"/>
       <c r="W280" t="n">
-        <v>0.791265993758999</v>
+        <v>0.8525406986059076</v>
       </c>
       <c r="X280" t="inlineStr"/>
       <c r="Y280" t="inlineStr"/>
       <c r="Z280" t="n">
-        <v>0.608936419471947</v>
+        <v>0.82408405687048</v>
       </c>
       <c r="AA280" t="n">
-        <v>0.496632411881188</v>
+        <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>5.5283124679868</v>
+        <v>13.8463590276134</v>
       </c>
       <c r="AC280" t="n">
-        <v>0.06487703465346541</v>
+        <v>0.06536710256410259</v>
       </c>
       <c r="AD280" t="n">
-        <v>2.68533988514851</v>
+        <v>9.698266819855361</v>
       </c>
       <c r="AE280" t="n">
-        <v>6.10167327953795</v>
+        <v>3.41887546252465</v>
       </c>
       <c r="AF280" t="n">
         <v>0</v>
       </c>
       <c r="AG280" t="n">
-        <v>0.810691586138614</v>
+        <v>1.23379041420118</v>
       </c>
       <c r="AH280" t="inlineStr"/>
       <c r="AI280" t="inlineStr"/>
@@ -26125,16 +26307,16 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CaNu</t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>CaNu_1</t>
+          <t>BoN_12</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -26142,80 +26324,82 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>19003</v>
+        <v>6007</v>
       </c>
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="K281" s="2" t="n">
-        <v>45630</v>
+        <v>45649</v>
       </c>
       <c r="L281" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M281" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="M281" t="n">
+        <v>20</v>
+      </c>
       <c r="N281" t="n">
-        <v>18.77</v>
+        <v>61.26</v>
       </c>
       <c r="O281" t="n">
-        <v>4.32</v>
+        <v>28.89</v>
       </c>
       <c r="P281" t="n">
-        <v>404.1618411</v>
+        <v>2273.071</v>
       </c>
       <c r="Q281" t="n">
-        <v>93.55598173611111</v>
+        <v>78.68020076150917</v>
       </c>
       <c r="R281" t="n">
-        <v>230.1545018646777</v>
+        <v>471.5964740450539</v>
       </c>
       <c r="S281" t="n">
-        <v>0.4125000000000001</v>
+        <v>0.178</v>
       </c>
       <c r="T281" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
       <c r="U281" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" t="n">
-        <v>0.7050569934332617</v>
+        <v>0.6589020209511743</v>
       </c>
       <c r="X281" t="inlineStr"/>
       <c r="Y281" t="inlineStr"/>
       <c r="Z281" t="n">
-        <v>0.905815394205729</v>
+        <v>0.535751518300654</v>
       </c>
       <c r="AA281" t="n">
-        <v>0.0122335712890625</v>
+        <v>0.100695831699346</v>
       </c>
       <c r="AB281" t="n">
-        <v>6.43516091178385</v>
+        <v>2.4234406</v>
       </c>
       <c r="AC281" t="n">
-        <v>0.0610385927734375</v>
+        <v>0.0496724725490196</v>
       </c>
       <c r="AD281" t="n">
-        <v>6.62207567382812</v>
+        <v>5.27523562875817</v>
       </c>
       <c r="AE281" t="n">
-        <v>8.93958169368489</v>
+        <v>0.939089979411765</v>
       </c>
       <c r="AF281" t="n">
-        <v>0.06749272167968751</v>
+        <v>0.109136456862745</v>
       </c>
       <c r="AG281" t="n">
-        <v>1.70840612597656</v>
+        <v>1.25907497745098</v>
       </c>
       <c r="AH281" t="inlineStr"/>
       <c r="AI281" t="inlineStr"/>
@@ -26250,18 +26434,18 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>2176</v>
+        <v>7626</v>
       </c>
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clarisia </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>racemosa</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="K282" s="2" t="n">
@@ -26270,60 +26454,62 @@
       <c r="L282" t="n">
         <v>1000</v>
       </c>
-      <c r="M282" t="inlineStr"/>
+      <c r="M282" t="n">
+        <v>20</v>
+      </c>
       <c r="N282" t="n">
-        <v>15.52</v>
+        <v>34.26</v>
       </c>
       <c r="O282" t="n">
-        <v>6.82</v>
+        <v>16.66</v>
       </c>
       <c r="P282" t="n">
-        <v>701.997</v>
+        <v>1240.024</v>
       </c>
       <c r="Q282" t="n">
-        <v>102.9321114369501</v>
+        <v>74.43121248499399</v>
       </c>
       <c r="R282" t="n">
-        <v>439.4329896907217</v>
+        <v>486.2813776999417</v>
       </c>
       <c r="S282" t="n">
-        <v>0.1893333333333334</v>
+        <v>0.191</v>
       </c>
       <c r="T282" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
       <c r="U282" t="n">
-        <v>0.585</v>
+        <v>0.788</v>
       </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" t="n">
-        <v>0.8525406986059076</v>
+        <v>0.7612917874918964</v>
       </c>
       <c r="X282" t="inlineStr"/>
       <c r="Y282" t="inlineStr"/>
       <c r="Z282" t="n">
-        <v>0.82408405687048</v>
+        <v>0.459120420727745</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>13.8463590276134</v>
+        <v>1.35529731384016</v>
       </c>
       <c r="AC282" t="n">
-        <v>0.06536710256410259</v>
+        <v>0.0410689356725146</v>
       </c>
       <c r="AD282" t="n">
-        <v>9.698266819855361</v>
+        <v>3.88617768745939</v>
       </c>
       <c r="AE282" t="n">
-        <v>3.41887546252465</v>
+        <v>0.765737796296296</v>
       </c>
       <c r="AF282" t="n">
-        <v>0</v>
+        <v>0.572714809941521</v>
       </c>
       <c r="AG282" t="n">
-        <v>1.23379041420118</v>
+        <v>1.11714552826511</v>
       </c>
       <c r="AH282" t="inlineStr"/>
       <c r="AI282" t="inlineStr"/>
@@ -26341,16 +26527,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t>CaNu</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BoN_12</t>
+          <t>CaNu_14</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -26358,80 +26544,82 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>6007</v>
+        <v>19017</v>
       </c>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="K283" s="2" t="n">
-        <v>45649</v>
+        <v>45628</v>
       </c>
       <c r="L283" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M283" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="M283" t="n">
+        <v>20</v>
+      </c>
       <c r="N283" t="n">
-        <v>61.26</v>
+        <v>17.85</v>
       </c>
       <c r="O283" t="n">
-        <v>28.89</v>
+        <v>5.1</v>
       </c>
       <c r="P283" t="n">
-        <v>2273.071</v>
+        <v>342.9727765</v>
       </c>
       <c r="Q283" t="n">
-        <v>78.68020076150917</v>
+        <v>67.24956401960785</v>
       </c>
       <c r="R283" t="n">
-        <v>471.5964740450539</v>
+        <v>285.7142857142857</v>
       </c>
       <c r="S283" t="n">
-        <v>0.178</v>
+        <v>0.4553333333333334</v>
       </c>
       <c r="T283" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="U283" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" t="n">
-        <v>0.6589020209511743</v>
+        <v>0.7708410921433626</v>
       </c>
       <c r="X283" t="inlineStr"/>
       <c r="Y283" t="inlineStr"/>
       <c r="Z283" t="n">
-        <v>0.535751518300654</v>
+        <v>0.781730154808959</v>
       </c>
       <c r="AA283" t="n">
-        <v>0.100695831699346</v>
+        <v>0.0359118833992095</v>
       </c>
       <c r="AB283" t="n">
-        <v>2.4234406</v>
+        <v>6.47114335342556</v>
       </c>
       <c r="AC283" t="n">
-        <v>0.0496724725490196</v>
+        <v>0.0496101175889328</v>
       </c>
       <c r="AD283" t="n">
-        <v>5.27523562875817</v>
+        <v>10.1591950187747</v>
       </c>
       <c r="AE283" t="n">
-        <v>0.939089979411765</v>
+        <v>5.48364941930171</v>
       </c>
       <c r="AF283" t="n">
-        <v>0.109136456862745</v>
+        <v>0.0331600918972331</v>
       </c>
       <c r="AG283" t="n">
-        <v>1.25907497745098</v>
+        <v>0.831675131422925</v>
       </c>
       <c r="AH283" t="inlineStr"/>
       <c r="AI283" t="inlineStr"/>
@@ -26449,16 +26637,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t>CaNu</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>BoN_12</t>
+          <t>CaNu_14</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -26466,80 +26654,82 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>7626</v>
+        <v>19018</v>
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="K284" s="2" t="n">
-        <v>45649</v>
+        <v>45628</v>
       </c>
       <c r="L284" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M284" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="M284" t="n">
+        <v>20</v>
+      </c>
       <c r="N284" t="n">
-        <v>34.26</v>
+        <v>18.45</v>
       </c>
       <c r="O284" t="n">
-        <v>16.66</v>
+        <v>4.96</v>
       </c>
       <c r="P284" t="n">
-        <v>1240.024</v>
+        <v>335.4892103</v>
       </c>
       <c r="Q284" t="n">
-        <v>74.43121248499399</v>
+        <v>67.63895368951613</v>
       </c>
       <c r="R284" t="n">
-        <v>486.2813776999417</v>
+        <v>268.8346883468835</v>
       </c>
       <c r="S284" t="n">
-        <v>0.191</v>
+        <v>0.4695</v>
       </c>
       <c r="T284" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="U284" t="n">
-        <v>0.788</v>
+        <v>0.585</v>
       </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" t="n">
-        <v>0.7612917874918964</v>
+        <v>1.201620835309509</v>
       </c>
       <c r="X284" t="inlineStr"/>
       <c r="Y284" t="inlineStr"/>
       <c r="Z284" t="n">
-        <v>0.459120420727745</v>
+        <v>0.84443941309987</v>
       </c>
       <c r="AA284" t="n">
-        <v>0</v>
+        <v>0.0141843822957198</v>
       </c>
       <c r="AB284" t="n">
-        <v>1.35529731384016</v>
+        <v>9.927820405317769</v>
       </c>
       <c r="AC284" t="n">
-        <v>0.0410689356725146</v>
+        <v>0.0573019445525292</v>
       </c>
       <c r="AD284" t="n">
-        <v>3.88617768745939</v>
+        <v>17.7740721585603</v>
       </c>
       <c r="AE284" t="n">
-        <v>0.765737796296296</v>
+        <v>4.28254724740597</v>
       </c>
       <c r="AF284" t="n">
-        <v>0.572714809941521</v>
+        <v>0.0242686138132294</v>
       </c>
       <c r="AG284" t="n">
-        <v>1.11714552826511</v>
+        <v>1.09683822081712</v>
       </c>
       <c r="AH284" t="inlineStr"/>
       <c r="AI284" t="inlineStr"/>
@@ -26557,12 +26747,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CaNu</t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>CaNu_14</t>
+          <t>BoN_14</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -26574,44 +26764,46 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>19017</v>
+        <v>3011</v>
       </c>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>racemosa</t>
         </is>
       </c>
       <c r="K285" s="2" t="n">
-        <v>45628</v>
+        <v>45616</v>
       </c>
       <c r="L285" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M285" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="M285" t="n">
+        <v>20</v>
+      </c>
       <c r="N285" t="n">
-        <v>17.85</v>
+        <v>25.52</v>
       </c>
       <c r="O285" t="n">
-        <v>5.1</v>
+        <v>11.67</v>
       </c>
       <c r="P285" t="n">
-        <v>342.9727765</v>
+        <v>1073.276</v>
       </c>
       <c r="Q285" t="n">
-        <v>67.24956401960785</v>
+        <v>91.96880891173952</v>
       </c>
       <c r="R285" t="n">
-        <v>285.7142857142857</v>
+        <v>457.2884012539185</v>
       </c>
       <c r="S285" t="n">
-        <v>0.4553333333333334</v>
+        <v>0.2325</v>
       </c>
       <c r="T285" t="n">
         <v>0.585</v>
@@ -26621,33 +26813,33 @@
       </c>
       <c r="V285" t="inlineStr"/>
       <c r="W285" t="n">
-        <v>0.7708410921433626</v>
+        <v>1.001615954553798</v>
       </c>
       <c r="X285" t="inlineStr"/>
       <c r="Y285" t="inlineStr"/>
       <c r="Z285" t="n">
-        <v>0.781730154808959</v>
+        <v>0.8158367908299869</v>
       </c>
       <c r="AA285" t="n">
-        <v>0.0359118833992095</v>
+        <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>6.47114335342556</v>
+        <v>18.7357618714859</v>
       </c>
       <c r="AC285" t="n">
-        <v>0.0496101175889328</v>
+        <v>0.0457575983935743</v>
       </c>
       <c r="AD285" t="n">
-        <v>10.1591950187747</v>
+        <v>7.77035797021419</v>
       </c>
       <c r="AE285" t="n">
-        <v>5.48364941930171</v>
+        <v>3.86308986044177</v>
       </c>
       <c r="AF285" t="n">
-        <v>0.0331600918972331</v>
+        <v>0</v>
       </c>
       <c r="AG285" t="n">
-        <v>0.831675131422925</v>
+        <v>1.11421847188755</v>
       </c>
       <c r="AH285" t="inlineStr"/>
       <c r="AI285" t="inlineStr"/>
@@ -26665,16 +26857,16 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>CaNu</t>
+          <t>SFNu</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>CaNu_14</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -26682,44 +26874,42 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>19018</v>
+        <v>88</v>
       </c>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hedyosmun </t>
-        </is>
-      </c>
+      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="K286" s="2" t="n">
-        <v>45628</v>
+        <v>45266</v>
       </c>
       <c r="L286" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M286" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="M286" t="n">
+        <v>20</v>
+      </c>
       <c r="N286" t="n">
-        <v>18.45</v>
+        <v>29.2</v>
       </c>
       <c r="O286" t="n">
-        <v>4.96</v>
+        <v>13.98</v>
       </c>
       <c r="P286" t="n">
-        <v>335.4892103</v>
+        <v>477.556</v>
       </c>
       <c r="Q286" t="n">
-        <v>67.63895368951613</v>
+        <v>34.15994277539342</v>
       </c>
       <c r="R286" t="n">
-        <v>268.8346883468835</v>
+        <v>478.7671232876712</v>
       </c>
       <c r="S286" t="n">
-        <v>0.4695</v>
+        <v>0.481</v>
       </c>
       <c r="T286" t="n">
         <v>0.585</v>
@@ -26729,33 +26919,37 @@
       </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" t="n">
-        <v>1.201620835309509</v>
-      </c>
-      <c r="X286" t="inlineStr"/>
-      <c r="Y286" t="inlineStr"/>
+        <v>1.453084630429005</v>
+      </c>
+      <c r="X286" t="n">
+        <v>490.27077</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>9.925939999999999</v>
+      </c>
       <c r="Z286" t="n">
-        <v>0.84443941309987</v>
+        <v>0.3022689226426593</v>
       </c>
       <c r="AA286" t="n">
-        <v>0.0141843822957198</v>
+        <v>0.07491061143778521</v>
       </c>
       <c r="AB286" t="n">
-        <v>9.927820405317769</v>
+        <v>1.011654000264961</v>
       </c>
       <c r="AC286" t="n">
-        <v>0.0573019445525292</v>
+        <v>0.04344123666451745</v>
       </c>
       <c r="AD286" t="n">
-        <v>17.7740721585603</v>
+        <v>2.849282673082712</v>
       </c>
       <c r="AE286" t="n">
-        <v>4.28254724740597</v>
+        <v>1.401589807905774</v>
       </c>
       <c r="AF286" t="n">
-        <v>0.0242686138132294</v>
+        <v>0.1011077059030895</v>
       </c>
       <c r="AG286" t="n">
-        <v>1.09683822081712</v>
+        <v>0.6435313779926263</v>
       </c>
       <c r="AH286" t="inlineStr"/>
       <c r="AI286" t="inlineStr"/>
@@ -26773,16 +26967,16 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t>SFNu</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>BoN_14</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -26790,44 +26984,42 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>3011</v>
+        <v>9096</v>
       </c>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clarisia </t>
-        </is>
-      </c>
+      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
-          <t>racemosa</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="K287" s="2" t="n">
-        <v>45616</v>
+        <v>45268</v>
       </c>
       <c r="L287" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M287" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="M287" t="n">
+        <v>20</v>
+      </c>
       <c r="N287" t="n">
-        <v>25.52</v>
+        <v>18.98</v>
       </c>
       <c r="O287" t="n">
-        <v>11.67</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P287" t="n">
-        <v>1073.276</v>
+        <v>349.395</v>
       </c>
       <c r="Q287" t="n">
-        <v>91.96880891173952</v>
+        <v>37.93648208469055</v>
       </c>
       <c r="R287" t="n">
-        <v>457.2884012539185</v>
+        <v>485.2476290832456</v>
       </c>
       <c r="S287" t="n">
-        <v>0.2325</v>
+        <v>0.5006666666666667</v>
       </c>
       <c r="T287" t="n">
         <v>0.585</v>
@@ -26837,33 +27029,37 @@
       </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" t="n">
-        <v>1.001615954553798</v>
-      </c>
-      <c r="X287" t="inlineStr"/>
-      <c r="Y287" t="inlineStr"/>
+        <v>1.558657409346628</v>
+      </c>
+      <c r="X287" t="n">
+        <v>494.83364</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>12.66312</v>
+      </c>
       <c r="Z287" t="n">
-        <v>0.8158367908299869</v>
+        <v>0.3625060659950419</v>
       </c>
       <c r="AA287" t="n">
-        <v>0</v>
+        <v>0.09466315171004382</v>
       </c>
       <c r="AB287" t="n">
-        <v>18.7357618714859</v>
+        <v>0.8955048151404393</v>
       </c>
       <c r="AC287" t="n">
-        <v>0.0457575983935743</v>
+        <v>0.06137497655135703</v>
       </c>
       <c r="AD287" t="n">
-        <v>7.77035797021419</v>
+        <v>2.773211836532035</v>
       </c>
       <c r="AE287" t="n">
-        <v>3.86308986044177</v>
+        <v>1.437625479152438</v>
       </c>
       <c r="AF287" t="n">
         <v>0</v>
       </c>
       <c r="AG287" t="n">
-        <v>1.11421847188755</v>
+        <v>0.5029688470154168</v>
       </c>
       <c r="AH287" t="inlineStr"/>
       <c r="AI287" t="inlineStr"/>
@@ -26886,11 +27082,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SFNu_1</t>
+          <t>SFNu_12</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -26898,7 +27094,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>88</v>
+        <v>721</v>
       </c>
       <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr"/>
@@ -26909,7 +27105,7 @@
         </is>
       </c>
       <c r="K288" s="2" t="n">
-        <v>45266</v>
+        <v>45283</v>
       </c>
       <c r="L288" t="n">
         <v>2000</v>
@@ -26918,22 +27114,22 @@
         <v>20</v>
       </c>
       <c r="N288" t="n">
-        <v>29.2</v>
+        <v>31.83</v>
       </c>
       <c r="O288" t="n">
-        <v>13.98</v>
+        <v>13.94</v>
       </c>
       <c r="P288" t="n">
-        <v>477.556</v>
+        <v>565.472</v>
       </c>
       <c r="Q288" t="n">
-        <v>34.15994277539342</v>
+        <v>40.56470588235294</v>
       </c>
       <c r="R288" t="n">
-        <v>478.7671232876712</v>
+        <v>437.9516179704681</v>
       </c>
       <c r="S288" t="n">
-        <v>0.481</v>
+        <v>0.536</v>
       </c>
       <c r="T288" t="n">
         <v>0.585</v>
@@ -26943,37 +27139,37 @@
       </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" t="n">
-        <v>1.453084630429005</v>
+        <v>1.572981354224899</v>
       </c>
       <c r="X288" t="n">
-        <v>490.27077</v>
+        <v>485.13672</v>
       </c>
       <c r="Y288" t="n">
-        <v>9.925939999999999</v>
+        <v>13.67501</v>
       </c>
       <c r="Z288" t="n">
-        <v>0.3022689226426593</v>
+        <v>0.4849510454859731</v>
       </c>
       <c r="AA288" t="n">
-        <v>0.07491061143778521</v>
+        <v>0.07202658542636962</v>
       </c>
       <c r="AB288" t="n">
-        <v>1.011654000264961</v>
+        <v>0.660988432929098</v>
       </c>
       <c r="AC288" t="n">
-        <v>0.04344123666451745</v>
+        <v>0.05690067620446475</v>
       </c>
       <c r="AD288" t="n">
-        <v>2.849282673082712</v>
+        <v>3.38871692156929</v>
       </c>
       <c r="AE288" t="n">
-        <v>1.401589807905774</v>
+        <v>1.475235308280186</v>
       </c>
       <c r="AF288" t="n">
-        <v>0.1011077059030895</v>
+        <v>0.01047223861793794</v>
       </c>
       <c r="AG288" t="n">
-        <v>0.6435313779926263</v>
+        <v>0.8623469556276475</v>
       </c>
       <c r="AH288" t="inlineStr"/>
       <c r="AI288" t="inlineStr"/>
@@ -26996,11 +27192,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>SFNu_1</t>
+          <t>SFNu_7</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -27008,7 +27204,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>9096</v>
+        <v>7994</v>
       </c>
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
@@ -27019,7 +27215,7 @@
         </is>
       </c>
       <c r="K289" s="2" t="n">
-        <v>45268</v>
+        <v>45275</v>
       </c>
       <c r="L289" t="n">
         <v>2000</v>
@@ -27028,22 +27224,22 @@
         <v>20</v>
       </c>
       <c r="N289" t="n">
-        <v>18.98</v>
+        <v>21.63</v>
       </c>
       <c r="O289" t="n">
-        <v>9.210000000000001</v>
+        <v>11.05</v>
       </c>
       <c r="P289" t="n">
-        <v>349.395</v>
+        <v>389.618</v>
       </c>
       <c r="Q289" t="n">
-        <v>37.93648208469055</v>
+        <v>35.25954751131221</v>
       </c>
       <c r="R289" t="n">
-        <v>485.2476290832456</v>
+        <v>510.8645399907537</v>
       </c>
       <c r="S289" t="n">
-        <v>0.5006666666666667</v>
+        <v>0.4531666666666667</v>
       </c>
       <c r="T289" t="n">
         <v>0.585</v>
@@ -27053,37 +27249,37 @@
       </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" t="n">
-        <v>1.558657409346628</v>
+        <v>1.429476647203707</v>
       </c>
       <c r="X289" t="n">
-        <v>494.83364</v>
+        <v>502.86171</v>
       </c>
       <c r="Y289" t="n">
-        <v>12.66312</v>
+        <v>9.312510000000001</v>
       </c>
       <c r="Z289" t="n">
-        <v>0.3625060659950419</v>
+        <v>0.3547881208221685</v>
       </c>
       <c r="AA289" t="n">
-        <v>0.09466315171004382</v>
+        <v>0.06275988448238888</v>
       </c>
       <c r="AB289" t="n">
-        <v>0.8955048151404393</v>
+        <v>1.095995840186212</v>
       </c>
       <c r="AC289" t="n">
-        <v>0.06137497655135703</v>
+        <v>0.04391447844078591</v>
       </c>
       <c r="AD289" t="n">
-        <v>2.773211836532035</v>
+        <v>3.077440353270796</v>
       </c>
       <c r="AE289" t="n">
-        <v>1.437625479152438</v>
+        <v>1.532295779471146</v>
       </c>
       <c r="AF289" t="n">
         <v>0</v>
       </c>
       <c r="AG289" t="n">
-        <v>0.5029688470154168</v>
+        <v>0.607201666864262</v>
       </c>
       <c r="AH289" t="inlineStr"/>
       <c r="AI289" t="inlineStr"/>
@@ -27106,11 +27302,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>SFNu_12</t>
+          <t>SFNu_17</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -27118,18 +27314,18 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>721</v>
+        <v>881</v>
       </c>
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="K290" s="2" t="n">
-        <v>45283</v>
+        <v>45290</v>
       </c>
       <c r="L290" t="n">
         <v>2000</v>
@@ -27138,22 +27334,22 @@
         <v>20</v>
       </c>
       <c r="N290" t="n">
-        <v>31.83</v>
+        <v>31.84</v>
       </c>
       <c r="O290" t="n">
-        <v>13.94</v>
+        <v>13.85</v>
       </c>
       <c r="P290" t="n">
-        <v>565.472</v>
+        <v>422.492</v>
       </c>
       <c r="Q290" t="n">
-        <v>40.56470588235294</v>
+        <v>30.50483754512636</v>
       </c>
       <c r="R290" t="n">
-        <v>437.9516179704681</v>
+        <v>434.9874371859297</v>
       </c>
       <c r="S290" t="n">
-        <v>0.536</v>
+        <v>0.626</v>
       </c>
       <c r="T290" t="n">
         <v>0.585</v>
@@ -27163,37 +27359,37 @@
       </c>
       <c r="V290" t="inlineStr"/>
       <c r="W290" t="n">
-        <v>1.572981354224899</v>
+        <v>1.800838181084796</v>
       </c>
       <c r="X290" t="n">
-        <v>485.13672</v>
+        <v>514.1052999999999</v>
       </c>
       <c r="Y290" t="n">
-        <v>13.67501</v>
+        <v>11.90928</v>
       </c>
       <c r="Z290" t="n">
-        <v>0.4849510454859731</v>
+        <v>0.7511820368610592</v>
       </c>
       <c r="AA290" t="n">
-        <v>0.07202658542636962</v>
+        <v>0.03535633972545513</v>
       </c>
       <c r="AB290" t="n">
-        <v>0.660988432929098</v>
+        <v>5.559157590754348</v>
       </c>
       <c r="AC290" t="n">
-        <v>0.05690067620446475</v>
+        <v>0.03404418706467198</v>
       </c>
       <c r="AD290" t="n">
-        <v>3.38871692156929</v>
+        <v>4.38668026168946</v>
       </c>
       <c r="AE290" t="n">
-        <v>1.475235308280186</v>
+        <v>1.951641594313444</v>
       </c>
       <c r="AF290" t="n">
-        <v>0.01047223861793794</v>
+        <v>0.1320176511445909</v>
       </c>
       <c r="AG290" t="n">
-        <v>0.8623469556276475</v>
+        <v>0.8176534495724884</v>
       </c>
       <c r="AH290" t="inlineStr"/>
       <c r="AI290" t="inlineStr"/>
@@ -27216,11 +27412,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>SFNu_7</t>
+          <t>SFNu_17</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -27228,7 +27424,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>7994</v>
+        <v>8954</v>
       </c>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
@@ -27239,7 +27435,7 @@
         </is>
       </c>
       <c r="K291" s="2" t="n">
-        <v>45275</v>
+        <v>45290</v>
       </c>
       <c r="L291" t="n">
         <v>2000</v>
@@ -27248,22 +27444,22 @@
         <v>20</v>
       </c>
       <c r="N291" t="n">
-        <v>21.63</v>
+        <v>37.94</v>
       </c>
       <c r="O291" t="n">
-        <v>11.05</v>
+        <v>17.75</v>
       </c>
       <c r="P291" t="n">
-        <v>389.618</v>
+        <v>770.355</v>
       </c>
       <c r="Q291" t="n">
-        <v>35.25954751131221</v>
+        <v>43.40028169014084</v>
       </c>
       <c r="R291" t="n">
-        <v>510.8645399907537</v>
+        <v>467.8439641539273</v>
       </c>
       <c r="S291" t="n">
-        <v>0.4531666666666667</v>
+        <v>0.4043333333333333</v>
       </c>
       <c r="T291" t="n">
         <v>0.585</v>
@@ -27273,37 +27469,37 @@
       </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" t="n">
-        <v>1.429476647203707</v>
+        <v>1.298173819152893</v>
       </c>
       <c r="X291" t="n">
-        <v>502.86171</v>
+        <v>503.96011</v>
       </c>
       <c r="Y291" t="n">
-        <v>9.312510000000001</v>
+        <v>10.54899</v>
       </c>
       <c r="Z291" t="n">
-        <v>0.3547881208221685</v>
+        <v>0.435002842237245</v>
       </c>
       <c r="AA291" t="n">
-        <v>0.06275988448238888</v>
+        <v>0.02151771985309472</v>
       </c>
       <c r="AB291" t="n">
-        <v>1.095995840186212</v>
+        <v>1.735047838399798</v>
       </c>
       <c r="AC291" t="n">
-        <v>0.04391447844078591</v>
+        <v>0.05546887529305437</v>
       </c>
       <c r="AD291" t="n">
-        <v>3.077440353270796</v>
+        <v>3.247971000957849</v>
       </c>
       <c r="AE291" t="n">
-        <v>1.532295779471146</v>
+        <v>1.07579931228647</v>
       </c>
       <c r="AF291" t="n">
         <v>0</v>
       </c>
       <c r="AG291" t="n">
-        <v>0.607201666864262</v>
+        <v>0.4725554111635041</v>
       </c>
       <c r="AH291" t="inlineStr"/>
       <c r="AI291" t="inlineStr"/>
@@ -27338,7 +27534,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>881</v>
+        <v>7645</v>
       </c>
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
@@ -27358,22 +27554,22 @@
         <v>20</v>
       </c>
       <c r="N292" t="n">
-        <v>31.84</v>
+        <v>52.58</v>
       </c>
       <c r="O292" t="n">
-        <v>13.85</v>
+        <v>23.72</v>
       </c>
       <c r="P292" t="n">
-        <v>422.492</v>
+        <v>765.008</v>
       </c>
       <c r="Q292" t="n">
-        <v>30.50483754512636</v>
+        <v>32.25160202360878</v>
       </c>
       <c r="R292" t="n">
-        <v>434.9874371859297</v>
+        <v>451.1220996576645</v>
       </c>
       <c r="S292" t="n">
-        <v>0.626</v>
+        <v>0.5835</v>
       </c>
       <c r="T292" t="n">
         <v>0.585</v>
@@ -27383,37 +27579,37 @@
       </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" t="n">
-        <v>1.800838181084796</v>
+        <v>1.68253300671982</v>
       </c>
       <c r="X292" t="n">
-        <v>514.1052999999999</v>
+        <v>501.49704</v>
       </c>
       <c r="Y292" t="n">
-        <v>11.90928</v>
+        <v>10.42012</v>
       </c>
       <c r="Z292" t="n">
-        <v>0.7511820368610592</v>
+        <v>0.6125897805332587</v>
       </c>
       <c r="AA292" t="n">
-        <v>0.03535633972545513</v>
+        <v>0.06432220725818644</v>
       </c>
       <c r="AB292" t="n">
-        <v>5.559157590754348</v>
+        <v>10.7680108606914</v>
       </c>
       <c r="AC292" t="n">
-        <v>0.03404418706467198</v>
+        <v>0.02926762778301256</v>
       </c>
       <c r="AD292" t="n">
-        <v>4.38668026168946</v>
+        <v>3.518306648273391</v>
       </c>
       <c r="AE292" t="n">
-        <v>1.951641594313444</v>
+        <v>3.742339742101213</v>
       </c>
       <c r="AF292" t="n">
-        <v>0.1320176511445909</v>
+        <v>0.08121815432355024</v>
       </c>
       <c r="AG292" t="n">
-        <v>0.8176534495724884</v>
+        <v>0.6001510992428434</v>
       </c>
       <c r="AH292" t="inlineStr"/>
       <c r="AI292" t="inlineStr"/>
@@ -27436,11 +27632,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>SFNu_17</t>
+          <t>SFNu_7</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -27448,18 +27644,18 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>8954</v>
+        <v>356</v>
       </c>
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="K293" s="2" t="n">
-        <v>45290</v>
+        <v>45275</v>
       </c>
       <c r="L293" t="n">
         <v>2000</v>
@@ -27468,22 +27664,22 @@
         <v>20</v>
       </c>
       <c r="N293" t="n">
-        <v>37.94</v>
+        <v>43.43</v>
       </c>
       <c r="O293" t="n">
-        <v>17.75</v>
+        <v>19.69</v>
       </c>
       <c r="P293" t="n">
-        <v>770.355</v>
+        <v>634.263</v>
       </c>
       <c r="Q293" t="n">
-        <v>43.40028169014084</v>
+        <v>32.21244286439817</v>
       </c>
       <c r="R293" t="n">
-        <v>467.8439641539273</v>
+        <v>453.3732443011743</v>
       </c>
       <c r="S293" t="n">
-        <v>0.4043333333333333</v>
+        <v>0.5373333333333333</v>
       </c>
       <c r="T293" t="n">
         <v>0.585</v>
@@ -27493,37 +27689,37 @@
       </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" t="n">
-        <v>1.298173819152893</v>
+        <v>1.871396872522203</v>
       </c>
       <c r="X293" t="n">
-        <v>503.96011</v>
+        <v>525.09987</v>
       </c>
       <c r="Y293" t="n">
-        <v>10.54899</v>
+        <v>12.99171</v>
       </c>
       <c r="Z293" t="n">
-        <v>0.435002842237245</v>
+        <v>0.7330294163502471</v>
       </c>
       <c r="AA293" t="n">
-        <v>0.02151771985309472</v>
+        <v>0.02341044632321697</v>
       </c>
       <c r="AB293" t="n">
-        <v>1.735047838399798</v>
+        <v>6.097811196499408</v>
       </c>
       <c r="AC293" t="n">
-        <v>0.05546887529305437</v>
+        <v>0.04172059697244149</v>
       </c>
       <c r="AD293" t="n">
-        <v>3.247971000957849</v>
+        <v>3.330271979229948</v>
       </c>
       <c r="AE293" t="n">
-        <v>1.07579931228647</v>
+        <v>2.416321375676183</v>
       </c>
       <c r="AF293" t="n">
-        <v>0</v>
+        <v>0.008358700613506674</v>
       </c>
       <c r="AG293" t="n">
-        <v>0.4725554111635041</v>
+        <v>0.6273144332028412</v>
       </c>
       <c r="AH293" t="inlineStr"/>
       <c r="AI293" t="inlineStr"/>
@@ -27546,11 +27742,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>SFNu_17</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -27558,7 +27754,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>7645</v>
+        <v>69</v>
       </c>
       <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr"/>
@@ -27569,7 +27765,7 @@
         </is>
       </c>
       <c r="K294" s="2" t="n">
-        <v>45290</v>
+        <v>45266</v>
       </c>
       <c r="L294" t="n">
         <v>2000</v>
@@ -27578,22 +27774,22 @@
         <v>20</v>
       </c>
       <c r="N294" t="n">
-        <v>52.58</v>
+        <v>37</v>
       </c>
       <c r="O294" t="n">
-        <v>23.72</v>
+        <v>16.22</v>
       </c>
       <c r="P294" t="n">
-        <v>765.008</v>
+        <v>622.667</v>
       </c>
       <c r="Q294" t="n">
-        <v>32.25160202360878</v>
+        <v>38.38884093711468</v>
       </c>
       <c r="R294" t="n">
-        <v>451.1220996576645</v>
+        <v>438.3783783783783</v>
       </c>
       <c r="S294" t="n">
-        <v>0.5835</v>
+        <v>0.5163333333333333</v>
       </c>
       <c r="T294" t="n">
         <v>0.585</v>
@@ -27603,37 +27799,37 @@
       </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" t="n">
-        <v>1.68253300671982</v>
+        <v>1.938241948620799</v>
       </c>
       <c r="X294" t="n">
-        <v>501.49704</v>
+        <v>522.5009200000001</v>
       </c>
       <c r="Y294" t="n">
-        <v>10.42012</v>
+        <v>15.57782</v>
       </c>
       <c r="Z294" t="n">
-        <v>0.6125897805332587</v>
+        <v>0.7330305807834134</v>
       </c>
       <c r="AA294" t="n">
-        <v>0.06432220725818644</v>
+        <v>0.03167074178634371</v>
       </c>
       <c r="AB294" t="n">
-        <v>10.7680108606914</v>
+        <v>4.67432647657722</v>
       </c>
       <c r="AC294" t="n">
-        <v>0.02926762778301256</v>
+        <v>0.06936965816675066</v>
       </c>
       <c r="AD294" t="n">
-        <v>3.518306648273391</v>
+        <v>4.47740697287675</v>
       </c>
       <c r="AE294" t="n">
-        <v>3.742339742101213</v>
+        <v>1.653474057529325</v>
       </c>
       <c r="AF294" t="n">
-        <v>0.08121815432355024</v>
+        <v>0.1096421257829917</v>
       </c>
       <c r="AG294" t="n">
-        <v>0.6001510992428434</v>
+        <v>0.9337543956289037</v>
       </c>
       <c r="AH294" t="inlineStr"/>
       <c r="AI294" t="inlineStr"/>
@@ -27656,11 +27852,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>SFNu_7</t>
+          <t>SFNu_12</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -27668,7 +27864,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>356</v>
+        <v>4894</v>
       </c>
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
@@ -27679,7 +27875,7 @@
         </is>
       </c>
       <c r="K295" s="2" t="n">
-        <v>45275</v>
+        <v>45283</v>
       </c>
       <c r="L295" t="n">
         <v>2000</v>
@@ -27688,22 +27884,22 @@
         <v>20</v>
       </c>
       <c r="N295" t="n">
-        <v>43.43</v>
+        <v>29.97</v>
       </c>
       <c r="O295" t="n">
-        <v>19.69</v>
+        <v>13.32</v>
       </c>
       <c r="P295" t="n">
-        <v>634.263</v>
+        <v>427.818</v>
       </c>
       <c r="Q295" t="n">
-        <v>32.21244286439817</v>
+        <v>32.11846846846846</v>
       </c>
       <c r="R295" t="n">
-        <v>453.3732443011743</v>
+        <v>444.4444444444445</v>
       </c>
       <c r="S295" t="n">
-        <v>0.5373333333333333</v>
+        <v>0.5693333333333334</v>
       </c>
       <c r="T295" t="n">
         <v>0.585</v>
@@ -27713,37 +27909,37 @@
       </c>
       <c r="V295" t="inlineStr"/>
       <c r="W295" t="n">
-        <v>1.871396872522203</v>
+        <v>1.804817054662093</v>
       </c>
       <c r="X295" t="n">
-        <v>525.09987</v>
+        <v>521.1967099999999</v>
       </c>
       <c r="Y295" t="n">
-        <v>12.99171</v>
+        <v>12.06294</v>
       </c>
       <c r="Z295" t="n">
-        <v>0.7330294163502471</v>
+        <v>0.8285671225617766</v>
       </c>
       <c r="AA295" t="n">
-        <v>0.02341044632321697</v>
+        <v>0.01614116365969542</v>
       </c>
       <c r="AB295" t="n">
-        <v>6.097811196499408</v>
+        <v>4.561378190818316</v>
       </c>
       <c r="AC295" t="n">
-        <v>0.04172059697244149</v>
+        <v>0.04723407003340536</v>
       </c>
       <c r="AD295" t="n">
-        <v>3.330271979229948</v>
+        <v>3.76334200686852</v>
       </c>
       <c r="AE295" t="n">
-        <v>2.416321375676183</v>
+        <v>2.212981654962291</v>
       </c>
       <c r="AF295" t="n">
-        <v>0.008358700613506674</v>
+        <v>0.04764741597787865</v>
       </c>
       <c r="AG295" t="n">
-        <v>0.6273144332028412</v>
+        <v>0.6999223603805288</v>
       </c>
       <c r="AH295" t="inlineStr"/>
       <c r="AI295" t="inlineStr"/>
@@ -27766,11 +27962,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>SFNu_1</t>
+          <t>SFNu_17</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -27778,18 +27974,18 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>69</v>
+        <v>902</v>
       </c>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="K296" s="2" t="n">
-        <v>45266</v>
+        <v>45290</v>
       </c>
       <c r="L296" t="n">
         <v>2000</v>
@@ -27798,22 +27994,22 @@
         <v>20</v>
       </c>
       <c r="N296" t="n">
-        <v>37</v>
+        <v>21.33</v>
       </c>
       <c r="O296" t="n">
-        <v>16.22</v>
+        <v>11.39</v>
       </c>
       <c r="P296" t="n">
-        <v>622.667</v>
+        <v>364.282</v>
       </c>
       <c r="Q296" t="n">
-        <v>38.38884093711468</v>
+        <v>31.98261633011413</v>
       </c>
       <c r="R296" t="n">
-        <v>438.3783783783783</v>
+        <v>533.9896858884201</v>
       </c>
       <c r="S296" t="n">
-        <v>0.5163333333333333</v>
+        <v>0.4651666666666667</v>
       </c>
       <c r="T296" t="n">
         <v>0.585</v>
@@ -27823,37 +28019,37 @@
       </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" t="n">
-        <v>1.938241948620799</v>
+        <v>1.326025934193974</v>
       </c>
       <c r="X296" t="n">
-        <v>522.5009200000001</v>
+        <v>516.5686000000001</v>
       </c>
       <c r="Y296" t="n">
-        <v>15.57782</v>
+        <v>28.82994</v>
       </c>
       <c r="Z296" t="n">
-        <v>0.7330305807834134</v>
+        <v>1.034293220205778</v>
       </c>
       <c r="AA296" t="n">
-        <v>0.03167074178634371</v>
+        <v>0.01312057038870004</v>
       </c>
       <c r="AB296" t="n">
-        <v>4.67432647657722</v>
+        <v>3.188852819659124</v>
       </c>
       <c r="AC296" t="n">
-        <v>0.06936965816675066</v>
+        <v>0.09915933720066963</v>
       </c>
       <c r="AD296" t="n">
-        <v>4.47740697287675</v>
+        <v>6.17453306928694</v>
       </c>
       <c r="AE296" t="n">
-        <v>1.653474057529325</v>
+        <v>2.605135208643901</v>
       </c>
       <c r="AF296" t="n">
-        <v>0.1096421257829917</v>
+        <v>0.2039762770512375</v>
       </c>
       <c r="AG296" t="n">
-        <v>0.9337543956289037</v>
+        <v>2.278914356063409</v>
       </c>
       <c r="AH296" t="inlineStr"/>
       <c r="AI296" t="inlineStr"/>
@@ -27888,14 +28084,14 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>4894</v>
+        <v>708</v>
       </c>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="K297" s="2" t="n">
@@ -27908,22 +28104,22 @@
         <v>20</v>
       </c>
       <c r="N297" t="n">
-        <v>29.97</v>
+        <v>21.05</v>
       </c>
       <c r="O297" t="n">
-        <v>13.32</v>
+        <v>10.51</v>
       </c>
       <c r="P297" t="n">
-        <v>427.818</v>
+        <v>372.801</v>
       </c>
       <c r="Q297" t="n">
-        <v>32.11846846846846</v>
+        <v>35.47107516650809</v>
       </c>
       <c r="R297" t="n">
-        <v>444.4444444444445</v>
+        <v>499.2874109263657</v>
       </c>
       <c r="S297" t="n">
-        <v>0.5693333333333334</v>
+        <v>0.4855</v>
       </c>
       <c r="T297" t="n">
         <v>0.585</v>
@@ -27933,37 +28129,37 @@
       </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" t="n">
-        <v>1.804817054662093</v>
+        <v>1.485976652001329</v>
       </c>
       <c r="X297" t="n">
-        <v>521.1967099999999</v>
+        <v>506.35567</v>
       </c>
       <c r="Y297" t="n">
-        <v>12.06294</v>
+        <v>11.34913</v>
       </c>
       <c r="Z297" t="n">
-        <v>0.8285671225617766</v>
+        <v>0.4332464644027982</v>
       </c>
       <c r="AA297" t="n">
-        <v>0.01614116365969542</v>
+        <v>0.0671946679347825</v>
       </c>
       <c r="AB297" t="n">
-        <v>4.561378190818316</v>
+        <v>0.4849596466528545</v>
       </c>
       <c r="AC297" t="n">
-        <v>0.04723407003340536</v>
+        <v>0.05396923218883296</v>
       </c>
       <c r="AD297" t="n">
-        <v>3.76334200686852</v>
+        <v>2.847428291812377</v>
       </c>
       <c r="AE297" t="n">
-        <v>2.212981654962291</v>
+        <v>0.7935578758482669</v>
       </c>
       <c r="AF297" t="n">
-        <v>0.04764741597787865</v>
+        <v>0.05788160464194943</v>
       </c>
       <c r="AG297" t="n">
-        <v>0.6999223603805288</v>
+        <v>1.074959982632039</v>
       </c>
       <c r="AH297" t="inlineStr"/>
       <c r="AI297" t="inlineStr"/>
@@ -27986,11 +28182,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>SFNu_17</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -27998,7 +28194,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>902</v>
+        <v>5812</v>
       </c>
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
@@ -28009,7 +28205,7 @@
         </is>
       </c>
       <c r="K298" s="2" t="n">
-        <v>45290</v>
+        <v>45297</v>
       </c>
       <c r="L298" t="n">
         <v>2000</v>
@@ -28018,22 +28214,22 @@
         <v>20</v>
       </c>
       <c r="N298" t="n">
-        <v>21.33</v>
+        <v>21.71</v>
       </c>
       <c r="O298" t="n">
-        <v>11.39</v>
+        <v>11.4</v>
       </c>
       <c r="P298" t="n">
-        <v>364.282</v>
+        <v>367.361</v>
       </c>
       <c r="Q298" t="n">
-        <v>31.98261633011413</v>
+        <v>32.22464912280702</v>
       </c>
       <c r="R298" t="n">
-        <v>533.9896858884201</v>
+        <v>525.103638876094</v>
       </c>
       <c r="S298" t="n">
-        <v>0.4651666666666667</v>
+        <v>0.4929999999999999</v>
       </c>
       <c r="T298" t="n">
         <v>0.585</v>
@@ -28043,37 +28239,37 @@
       </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" t="n">
-        <v>1.326025934193974</v>
+        <v>1.369263027067273</v>
       </c>
       <c r="X298" t="n">
-        <v>516.5686000000001</v>
+        <v>502.02518</v>
       </c>
       <c r="Y298" t="n">
-        <v>28.82994</v>
+        <v>11.75361</v>
       </c>
       <c r="Z298" t="n">
-        <v>1.034293220205778</v>
+        <v>0.3301460673610775</v>
       </c>
       <c r="AA298" t="n">
-        <v>0.01312057038870004</v>
+        <v>0.1763737041152352</v>
       </c>
       <c r="AB298" t="n">
-        <v>3.188852819659124</v>
+        <v>0.7334009701884723</v>
       </c>
       <c r="AC298" t="n">
-        <v>0.09915933720066963</v>
+        <v>0.04686403088603966</v>
       </c>
       <c r="AD298" t="n">
-        <v>6.17453306928694</v>
+        <v>2.696832020177923</v>
       </c>
       <c r="AE298" t="n">
-        <v>2.605135208643901</v>
+        <v>0.9677041198252244</v>
       </c>
       <c r="AF298" t="n">
-        <v>0.2039762770512375</v>
+        <v>0.1383421608311446</v>
       </c>
       <c r="AG298" t="n">
-        <v>2.278914356063409</v>
+        <v>0.8176350567429458</v>
       </c>
       <c r="AH298" t="inlineStr"/>
       <c r="AI298" t="inlineStr"/>
@@ -28096,11 +28292,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>SFNu_12</t>
+          <t>SFNu_7</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -28108,7 +28304,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>708</v>
+        <v>333</v>
       </c>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
@@ -28119,7 +28315,7 @@
         </is>
       </c>
       <c r="K299" s="2" t="n">
-        <v>45283</v>
+        <v>45276</v>
       </c>
       <c r="L299" t="n">
         <v>2000</v>
@@ -28128,22 +28324,22 @@
         <v>20</v>
       </c>
       <c r="N299" t="n">
-        <v>21.05</v>
+        <v>17</v>
       </c>
       <c r="O299" t="n">
-        <v>10.51</v>
+        <v>8.01</v>
       </c>
       <c r="P299" t="n">
-        <v>372.801</v>
+        <v>272.311</v>
       </c>
       <c r="Q299" t="n">
-        <v>35.47107516650809</v>
+        <v>33.99637952559301</v>
       </c>
       <c r="R299" t="n">
-        <v>499.2874109263657</v>
+        <v>471.1764705882353</v>
       </c>
       <c r="S299" t="n">
-        <v>0.4855</v>
+        <v>0.4738333333333333</v>
       </c>
       <c r="T299" t="n">
         <v>0.585</v>
@@ -28153,37 +28349,37 @@
       </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" t="n">
-        <v>1.485976652001329</v>
+        <v>1.482528294901005</v>
       </c>
       <c r="X299" t="n">
-        <v>506.35567</v>
+        <v>504.0885200000001</v>
       </c>
       <c r="Y299" t="n">
-        <v>11.34913</v>
+        <v>10.92129</v>
       </c>
       <c r="Z299" t="n">
-        <v>0.4332464644027982</v>
+        <v>0.4090062180236554</v>
       </c>
       <c r="AA299" t="n">
-        <v>0.0671946679347825</v>
+        <v>0.05578735823071405</v>
       </c>
       <c r="AB299" t="n">
-        <v>0.4849596466528545</v>
+        <v>0.9597373511768502</v>
       </c>
       <c r="AC299" t="n">
-        <v>0.05396923218883296</v>
+        <v>0.04497490587675609</v>
       </c>
       <c r="AD299" t="n">
-        <v>2.847428291812377</v>
+        <v>3.672252156726751</v>
       </c>
       <c r="AE299" t="n">
-        <v>0.7935578758482669</v>
+        <v>1.14677420294889</v>
       </c>
       <c r="AF299" t="n">
-        <v>0.05788160464194943</v>
+        <v>0.1152405722488314</v>
       </c>
       <c r="AG299" t="n">
-        <v>1.074959982632039</v>
+        <v>0.6728416599837868</v>
       </c>
       <c r="AH299" t="inlineStr"/>
       <c r="AI299" t="inlineStr"/>
@@ -28206,11 +28402,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>SFNu_1</t>
+          <t>SFNu_17</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -28218,18 +28414,18 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>5812</v>
+        <v>4932</v>
       </c>
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="K300" s="2" t="n">
-        <v>45297</v>
+        <v>45290</v>
       </c>
       <c r="L300" t="n">
         <v>2000</v>
@@ -28238,22 +28434,22 @@
         <v>20</v>
       </c>
       <c r="N300" t="n">
-        <v>21.71</v>
+        <v>44.48</v>
       </c>
       <c r="O300" t="n">
-        <v>11.4</v>
+        <v>18.83</v>
       </c>
       <c r="P300" t="n">
-        <v>367.361</v>
+        <v>696.715</v>
       </c>
       <c r="Q300" t="n">
-        <v>32.22464912280702</v>
+        <v>37.00026553372279</v>
       </c>
       <c r="R300" t="n">
-        <v>525.103638876094</v>
+        <v>423.3363309352518</v>
       </c>
       <c r="S300" t="n">
-        <v>0.4929999999999999</v>
+        <v>0.5528333333333334</v>
       </c>
       <c r="T300" t="n">
         <v>0.585</v>
@@ -28263,37 +28459,37 @@
       </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" t="n">
-        <v>1.369263027067273</v>
+        <v>1.629481359022522</v>
       </c>
       <c r="X300" t="n">
-        <v>502.02518</v>
+        <v>484.5468100000001</v>
       </c>
       <c r="Y300" t="n">
-        <v>11.75361</v>
+        <v>12.8539</v>
       </c>
       <c r="Z300" t="n">
-        <v>0.3301460673610775</v>
+        <v>0.6299664353692545</v>
       </c>
       <c r="AA300" t="n">
-        <v>0.1763737041152352</v>
+        <v>5.353827909284697</v>
       </c>
       <c r="AB300" t="n">
-        <v>0.7334009701884723</v>
+        <v>1.67115320519117</v>
       </c>
       <c r="AC300" t="n">
-        <v>0.04686403088603966</v>
+        <v>0.04593621996896467</v>
       </c>
       <c r="AD300" t="n">
-        <v>2.696832020177923</v>
+        <v>8.575883768788922</v>
       </c>
       <c r="AE300" t="n">
-        <v>0.9677041198252244</v>
+        <v>2.803384202125449</v>
       </c>
       <c r="AF300" t="n">
-        <v>0.1383421608311446</v>
+        <v>0.07090254958449208</v>
       </c>
       <c r="AG300" t="n">
-        <v>0.8176350567429458</v>
+        <v>0.940845396234007</v>
       </c>
       <c r="AH300" t="inlineStr"/>
       <c r="AI300" t="inlineStr"/>
@@ -28316,11 +28512,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>SFNu_7</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -28328,7 +28524,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>333</v>
+        <v>96</v>
       </c>
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
@@ -28339,7 +28535,7 @@
         </is>
       </c>
       <c r="K301" s="2" t="n">
-        <v>45276</v>
+        <v>45266</v>
       </c>
       <c r="L301" t="n">
         <v>2000</v>
@@ -28348,22 +28544,22 @@
         <v>20</v>
       </c>
       <c r="N301" t="n">
-        <v>17</v>
+        <v>22.07</v>
       </c>
       <c r="O301" t="n">
-        <v>8.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="P301" t="n">
-        <v>272.311</v>
+        <v>412.252</v>
       </c>
       <c r="Q301" t="n">
-        <v>33.99637952559301</v>
+        <v>45.65359911406424</v>
       </c>
       <c r="R301" t="n">
-        <v>471.1764705882353</v>
+        <v>409.1526959673765</v>
       </c>
       <c r="S301" t="n">
-        <v>0.4738333333333333</v>
+        <v>0.5057999999999999</v>
       </c>
       <c r="T301" t="n">
         <v>0.585</v>
@@ -28373,37 +28569,37 @@
       </c>
       <c r="V301" t="inlineStr"/>
       <c r="W301" t="n">
-        <v>1.482528294901005</v>
+        <v>1.781474329675282</v>
       </c>
       <c r="X301" t="n">
-        <v>504.0885200000001</v>
+        <v>495.60219</v>
       </c>
       <c r="Y301" t="n">
-        <v>10.92129</v>
+        <v>12.74179</v>
       </c>
       <c r="Z301" t="n">
-        <v>0.4090062180236554</v>
+        <v>0.3602235709573822</v>
       </c>
       <c r="AA301" t="n">
-        <v>0.05578735823071405</v>
+        <v>0.1504766568838256</v>
       </c>
       <c r="AB301" t="n">
-        <v>0.9597373511768502</v>
+        <v>0.8966191294944377</v>
       </c>
       <c r="AC301" t="n">
-        <v>0.04497490587675609</v>
+        <v>0.0398164595408567</v>
       </c>
       <c r="AD301" t="n">
-        <v>3.672252156726751</v>
+        <v>4.166705700327024</v>
       </c>
       <c r="AE301" t="n">
-        <v>1.14677420294889</v>
+        <v>1.428129970001396</v>
       </c>
       <c r="AF301" t="n">
-        <v>0.1152405722488314</v>
+        <v>0</v>
       </c>
       <c r="AG301" t="n">
-        <v>0.6728416599837868</v>
+        <v>0.5953654546153796</v>
       </c>
       <c r="AH301" t="inlineStr"/>
       <c r="AI301" t="inlineStr"/>
@@ -28426,11 +28622,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>SFNu_17</t>
+          <t>SFNu_12</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -28438,18 +28634,18 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>4932</v>
+        <v>729</v>
       </c>
       <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Alchornea lojaensis</t>
+          <t>Myrcia sp nov</t>
         </is>
       </c>
       <c r="K302" s="2" t="n">
-        <v>45290</v>
+        <v>45283</v>
       </c>
       <c r="L302" t="n">
         <v>2000</v>
@@ -28458,22 +28654,22 @@
         <v>20</v>
       </c>
       <c r="N302" t="n">
-        <v>44.48</v>
+        <v>25.17</v>
       </c>
       <c r="O302" t="n">
-        <v>18.83</v>
+        <v>12.87</v>
       </c>
       <c r="P302" t="n">
-        <v>696.715</v>
+        <v>406.956</v>
       </c>
       <c r="Q302" t="n">
-        <v>37.00026553372279</v>
+        <v>31.62051282051283</v>
       </c>
       <c r="R302" t="n">
-        <v>423.3363309352518</v>
+        <v>511.3230035756853</v>
       </c>
       <c r="S302" t="n">
-        <v>0.5528333333333334</v>
+        <v>0.4928333333333334</v>
       </c>
       <c r="T302" t="n">
         <v>0.585</v>
@@ -28483,37 +28679,37 @@
       </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" t="n">
-        <v>1.629481359022522</v>
+        <v>1.542476656798953</v>
       </c>
       <c r="X302" t="n">
-        <v>484.5468100000001</v>
+        <v>498.8081</v>
       </c>
       <c r="Y302" t="n">
-        <v>12.8539</v>
+        <v>9.79006</v>
       </c>
       <c r="Z302" t="n">
-        <v>0.6299664353692545</v>
+        <v>0.3894930957229775</v>
       </c>
       <c r="AA302" t="n">
-        <v>5.353827909284697</v>
+        <v>0.07896420668038333</v>
       </c>
       <c r="AB302" t="n">
-        <v>1.67115320519117</v>
+        <v>0.6335766588293329</v>
       </c>
       <c r="AC302" t="n">
-        <v>0.04593621996896467</v>
+        <v>0.0536149248729403</v>
       </c>
       <c r="AD302" t="n">
-        <v>8.575883768788922</v>
+        <v>2.648745629382531</v>
       </c>
       <c r="AE302" t="n">
-        <v>2.803384202125449</v>
+        <v>0.9252929922084216</v>
       </c>
       <c r="AF302" t="n">
-        <v>0.07090254958449208</v>
+        <v>0.1171130805248962</v>
       </c>
       <c r="AG302" t="n">
-        <v>0.940845396234007</v>
+        <v>0.8223695401235284</v>
       </c>
       <c r="AH302" t="inlineStr"/>
       <c r="AI302" t="inlineStr"/>
@@ -28536,11 +28732,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>SFNu_1</t>
+          <t>SFNu_7</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -28548,7 +28744,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>96</v>
+        <v>6992</v>
       </c>
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
@@ -28559,7 +28755,7 @@
         </is>
       </c>
       <c r="K303" s="2" t="n">
-        <v>45266</v>
+        <v>45275</v>
       </c>
       <c r="L303" t="n">
         <v>2000</v>
@@ -28568,22 +28764,22 @@
         <v>20</v>
       </c>
       <c r="N303" t="n">
-        <v>22.07</v>
+        <v>14.18</v>
       </c>
       <c r="O303" t="n">
-        <v>9.029999999999999</v>
+        <v>6.58</v>
       </c>
       <c r="P303" t="n">
-        <v>412.252</v>
+        <v>250.543</v>
       </c>
       <c r="Q303" t="n">
-        <v>45.65359911406424</v>
+        <v>38.07644376899696</v>
       </c>
       <c r="R303" t="n">
-        <v>409.1526959673765</v>
+        <v>464.033850493653</v>
       </c>
       <c r="S303" t="n">
-        <v>0.5057999999999999</v>
+        <v>0.4511666666666667</v>
       </c>
       <c r="T303" t="n">
         <v>0.585</v>
@@ -28593,37 +28789,37 @@
       </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" t="n">
-        <v>1.781474329675282</v>
+        <v>1.573246612463385</v>
       </c>
       <c r="X303" t="n">
-        <v>495.60219</v>
+        <v>497.12307</v>
       </c>
       <c r="Y303" t="n">
-        <v>12.74179</v>
+        <v>10.16024</v>
       </c>
       <c r="Z303" t="n">
-        <v>0.3602235709573822</v>
+        <v>0.4436594649764164</v>
       </c>
       <c r="AA303" t="n">
-        <v>0.1504766568838256</v>
+        <v>0.06803443922798549</v>
       </c>
       <c r="AB303" t="n">
-        <v>0.8966191294944377</v>
+        <v>0.9992243656932256</v>
       </c>
       <c r="AC303" t="n">
-        <v>0.0398164595408567</v>
+        <v>0.03952134576962973</v>
       </c>
       <c r="AD303" t="n">
-        <v>4.166705700327024</v>
+        <v>4.969056241840997</v>
       </c>
       <c r="AE303" t="n">
-        <v>1.428129970001396</v>
+        <v>0.9580686381773037</v>
       </c>
       <c r="AF303" t="n">
-        <v>0</v>
+        <v>0.02051497620042958</v>
       </c>
       <c r="AG303" t="n">
-        <v>0.5953654546153796</v>
+        <v>0.6389589434154307</v>
       </c>
       <c r="AH303" t="inlineStr"/>
       <c r="AI303" t="inlineStr"/>
@@ -28646,11 +28842,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>SFNu_12</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -28658,7 +28854,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>729</v>
+        <v>90</v>
       </c>
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
@@ -28669,7 +28865,7 @@
         </is>
       </c>
       <c r="K304" s="2" t="n">
-        <v>45283</v>
+        <v>45266</v>
       </c>
       <c r="L304" t="n">
         <v>2000</v>
@@ -28678,22 +28874,22 @@
         <v>20</v>
       </c>
       <c r="N304" t="n">
-        <v>25.17</v>
+        <v>20.4</v>
       </c>
       <c r="O304" t="n">
-        <v>12.87</v>
+        <v>10.3</v>
       </c>
       <c r="P304" t="n">
-        <v>406.956</v>
+        <v>355.274</v>
       </c>
       <c r="Q304" t="n">
-        <v>31.62051282051283</v>
+        <v>34.4926213592233</v>
       </c>
       <c r="R304" t="n">
-        <v>511.3230035756853</v>
+        <v>504.9019607843138</v>
       </c>
       <c r="S304" t="n">
-        <v>0.4928333333333334</v>
+        <v>0.4769999999999999</v>
       </c>
       <c r="T304" t="n">
         <v>0.585</v>
@@ -28703,37 +28899,37 @@
       </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" t="n">
-        <v>1.542476656798953</v>
+        <v>1.521521255958519</v>
       </c>
       <c r="X304" t="n">
-        <v>498.8081</v>
+        <v>507.07012</v>
       </c>
       <c r="Y304" t="n">
-        <v>9.79006</v>
+        <v>10.73803</v>
       </c>
       <c r="Z304" t="n">
-        <v>0.3894930957229775</v>
+        <v>0.324984654635016</v>
       </c>
       <c r="AA304" t="n">
-        <v>0.07896420668038333</v>
+        <v>0.1589347534440449</v>
       </c>
       <c r="AB304" t="n">
-        <v>0.6335766588293329</v>
+        <v>0.960796961042731</v>
       </c>
       <c r="AC304" t="n">
-        <v>0.0536149248729403</v>
+        <v>0.05708870945842138</v>
       </c>
       <c r="AD304" t="n">
-        <v>2.648745629382531</v>
+        <v>2.078787911790655</v>
       </c>
       <c r="AE304" t="n">
-        <v>0.9252929922084216</v>
+        <v>1.186882457029126</v>
       </c>
       <c r="AF304" t="n">
-        <v>0.1171130805248962</v>
+        <v>0.1766401930579916</v>
       </c>
       <c r="AG304" t="n">
-        <v>0.8223695401235284</v>
+        <v>0.6721646921959057</v>
       </c>
       <c r="AH304" t="inlineStr"/>
       <c r="AI304" t="inlineStr"/>
@@ -28768,7 +28964,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>6992</v>
+        <v>341</v>
       </c>
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
@@ -28788,22 +28984,22 @@
         <v>20</v>
       </c>
       <c r="N305" t="n">
-        <v>14.18</v>
+        <v>21.51</v>
       </c>
       <c r="O305" t="n">
-        <v>6.58</v>
+        <v>10.04</v>
       </c>
       <c r="P305" t="n">
-        <v>250.543</v>
+        <v>366.894</v>
       </c>
       <c r="Q305" t="n">
-        <v>38.07644376899696</v>
+        <v>36.54322709163347</v>
       </c>
       <c r="R305" t="n">
-        <v>464.033850493653</v>
+        <v>466.7596466759646</v>
       </c>
       <c r="S305" t="n">
-        <v>0.4511666666666667</v>
+        <v>0.4885</v>
       </c>
       <c r="T305" t="n">
         <v>0.585</v>
@@ -28813,37 +29009,37 @@
       </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" t="n">
-        <v>1.573246612463385</v>
+        <v>1.620993095390954</v>
       </c>
       <c r="X305" t="n">
-        <v>497.12307</v>
+        <v>500.85838</v>
       </c>
       <c r="Y305" t="n">
-        <v>10.16024</v>
+        <v>8.93587</v>
       </c>
       <c r="Z305" t="n">
-        <v>0.4436594649764164</v>
+        <v>0.4191162035677621</v>
       </c>
       <c r="AA305" t="n">
-        <v>0.06803443922798549</v>
+        <v>0.04559581779906421</v>
       </c>
       <c r="AB305" t="n">
-        <v>0.9992243656932256</v>
+        <v>1.323229487492985</v>
       </c>
       <c r="AC305" t="n">
-        <v>0.03952134576962973</v>
+        <v>0.03018458681571652</v>
       </c>
       <c r="AD305" t="n">
-        <v>4.969056241840997</v>
+        <v>3.785437907279968</v>
       </c>
       <c r="AE305" t="n">
-        <v>0.9580686381773037</v>
+        <v>1.190580552858766</v>
       </c>
       <c r="AF305" t="n">
-        <v>0.02051497620042958</v>
+        <v>0.2311756989151668</v>
       </c>
       <c r="AG305" t="n">
-        <v>0.6389589434154307</v>
+        <v>0.645384356401851</v>
       </c>
       <c r="AH305" t="inlineStr"/>
       <c r="AI305" t="inlineStr"/>
@@ -28866,11 +29062,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SFNu_1</t>
+          <t>SFNu_17</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -28878,7 +29074,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>90</v>
+        <v>4933</v>
       </c>
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
@@ -28889,7 +29085,7 @@
         </is>
       </c>
       <c r="K306" s="2" t="n">
-        <v>45266</v>
+        <v>45294</v>
       </c>
       <c r="L306" t="n">
         <v>2000</v>
@@ -28898,22 +29094,22 @@
         <v>20</v>
       </c>
       <c r="N306" t="n">
-        <v>20.4</v>
+        <v>17.09</v>
       </c>
       <c r="O306" t="n">
-        <v>10.3</v>
+        <v>8.77</v>
       </c>
       <c r="P306" t="n">
-        <v>355.274</v>
+        <v>282.598</v>
       </c>
       <c r="Q306" t="n">
-        <v>34.4926213592233</v>
+        <v>32.22326111744584</v>
       </c>
       <c r="R306" t="n">
-        <v>504.9019607843138</v>
+        <v>513.16559391457</v>
       </c>
       <c r="S306" t="n">
-        <v>0.4769999999999999</v>
+        <v>0.4626666666666666</v>
       </c>
       <c r="T306" t="n">
         <v>0.585</v>
@@ -28923,37 +29119,37 @@
       </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" t="n">
-        <v>1.521521255958519</v>
+        <v>1.524173838343385</v>
       </c>
       <c r="X306" t="n">
-        <v>507.07012</v>
+        <v>498.50624</v>
       </c>
       <c r="Y306" t="n">
-        <v>10.73803</v>
+        <v>10.54628</v>
       </c>
       <c r="Z306" t="n">
-        <v>0.324984654635016</v>
+        <v>0.4231620695175342</v>
       </c>
       <c r="AA306" t="n">
-        <v>0.1589347534440449</v>
+        <v>0.07741346507634229</v>
       </c>
       <c r="AB306" t="n">
-        <v>0.960796961042731</v>
+        <v>0.8864310941421033</v>
       </c>
       <c r="AC306" t="n">
-        <v>0.05708870945842138</v>
+        <v>0.04795257679620588</v>
       </c>
       <c r="AD306" t="n">
-        <v>2.078787911790655</v>
+        <v>3.457335577835881</v>
       </c>
       <c r="AE306" t="n">
-        <v>1.186882457029126</v>
+        <v>0.6643245927708848</v>
       </c>
       <c r="AF306" t="n">
-        <v>0.1766401930579916</v>
+        <v>0</v>
       </c>
       <c r="AG306" t="n">
-        <v>0.6721646921959057</v>
+        <v>0.4601034607357175</v>
       </c>
       <c r="AH306" t="inlineStr"/>
       <c r="AI306" t="inlineStr"/>
@@ -28976,11 +29172,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>SFNu_7</t>
+          <t>SFNu_12</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -28988,18 +29184,18 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>341</v>
+        <v>7594</v>
       </c>
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="K307" s="2" t="n">
-        <v>45275</v>
+        <v>45283</v>
       </c>
       <c r="L307" t="n">
         <v>2000</v>
@@ -29008,22 +29204,22 @@
         <v>20</v>
       </c>
       <c r="N307" t="n">
-        <v>21.51</v>
+        <v>34.95</v>
       </c>
       <c r="O307" t="n">
-        <v>10.04</v>
+        <v>15.19</v>
       </c>
       <c r="P307" t="n">
-        <v>366.894</v>
+        <v>482.797</v>
       </c>
       <c r="Q307" t="n">
-        <v>36.54322709163347</v>
+        <v>31.78387096774194</v>
       </c>
       <c r="R307" t="n">
-        <v>466.7596466759646</v>
+        <v>434.620886981402</v>
       </c>
       <c r="S307" t="n">
-        <v>0.4885</v>
+        <v>0.5846666666666667</v>
       </c>
       <c r="T307" t="n">
         <v>0.585</v>
@@ -29033,37 +29229,37 @@
       </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" t="n">
-        <v>1.620993095390954</v>
+        <v>1.645927369808684</v>
       </c>
       <c r="X307" t="n">
-        <v>500.85838</v>
+        <v>520.02068</v>
       </c>
       <c r="Y307" t="n">
-        <v>8.93587</v>
+        <v>15.24436</v>
       </c>
       <c r="Z307" t="n">
-        <v>0.4191162035677621</v>
+        <v>1.060681081061475</v>
       </c>
       <c r="AA307" t="n">
-        <v>0.04559581779906421</v>
+        <v>0.0325619423628069</v>
       </c>
       <c r="AB307" t="n">
-        <v>1.323229487492985</v>
+        <v>2.891816589846828</v>
       </c>
       <c r="AC307" t="n">
-        <v>0.03018458681571652</v>
+        <v>0.02768839215525221</v>
       </c>
       <c r="AD307" t="n">
-        <v>3.785437907279968</v>
+        <v>5.334707698656458</v>
       </c>
       <c r="AE307" t="n">
-        <v>1.190580552858766</v>
+        <v>2.029258417161623</v>
       </c>
       <c r="AF307" t="n">
-        <v>0.2311756989151668</v>
+        <v>0.03049873209915185</v>
       </c>
       <c r="AG307" t="n">
-        <v>0.645384356401851</v>
+        <v>0.7125169065607428</v>
       </c>
       <c r="AH307" t="inlineStr"/>
       <c r="AI307" t="inlineStr"/>
@@ -29086,11 +29282,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>SFNu_17</t>
+          <t>SFNu_7</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -29098,18 +29294,18 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>4933</v>
+        <v>6994</v>
       </c>
       <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Myrcia sp nov</t>
+          <t>Alchornea lojaensis</t>
         </is>
       </c>
       <c r="K308" s="2" t="n">
-        <v>45294</v>
+        <v>45275</v>
       </c>
       <c r="L308" t="n">
         <v>2000</v>
@@ -29118,22 +29314,22 @@
         <v>20</v>
       </c>
       <c r="N308" t="n">
-        <v>17.09</v>
+        <v>25.42</v>
       </c>
       <c r="O308" t="n">
-        <v>8.77</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="P308" t="n">
-        <v>282.598</v>
+        <v>414.662</v>
       </c>
       <c r="Q308" t="n">
-        <v>32.22326111744584</v>
+        <v>41.63273092369477</v>
       </c>
       <c r="R308" t="n">
-        <v>513.16559391457</v>
+        <v>391.8174665617624</v>
       </c>
       <c r="S308" t="n">
-        <v>0.4626666666666666</v>
+        <v>0.5203333333333333</v>
       </c>
       <c r="T308" t="n">
         <v>0.585</v>
@@ -29143,37 +29339,37 @@
       </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" t="n">
-        <v>1.524173838343385</v>
+        <v>1.627624551353116</v>
       </c>
       <c r="X308" t="n">
-        <v>498.50624</v>
+        <v>517.31335</v>
       </c>
       <c r="Y308" t="n">
-        <v>10.54628</v>
+        <v>14.5382</v>
       </c>
       <c r="Z308" t="n">
-        <v>0.4231620695175342</v>
+        <v>0.876007634737751</v>
       </c>
       <c r="AA308" t="n">
-        <v>0.07741346507634229</v>
+        <v>0.08882237222577244</v>
       </c>
       <c r="AB308" t="n">
-        <v>0.8864310941421033</v>
+        <v>4.826290506065171</v>
       </c>
       <c r="AC308" t="n">
-        <v>0.04795257679620588</v>
+        <v>0.04264856647420304</v>
       </c>
       <c r="AD308" t="n">
-        <v>3.457335577835881</v>
+        <v>5.52778822181687</v>
       </c>
       <c r="AE308" t="n">
-        <v>0.6643245927708848</v>
+        <v>3.169718443828744</v>
       </c>
       <c r="AF308" t="n">
         <v>0</v>
       </c>
       <c r="AG308" t="n">
-        <v>0.4601034607357175</v>
+        <v>0.7328988444232435</v>
       </c>
       <c r="AH308" t="inlineStr"/>
       <c r="AI308" t="inlineStr"/>
@@ -29196,11 +29392,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>SFNu_12</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -29208,7 +29404,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>7594</v>
+        <v>92</v>
       </c>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
@@ -29219,7 +29415,7 @@
         </is>
       </c>
       <c r="K309" s="2" t="n">
-        <v>45283</v>
+        <v>45266</v>
       </c>
       <c r="L309" t="n">
         <v>2000</v>
@@ -29228,22 +29424,22 @@
         <v>20</v>
       </c>
       <c r="N309" t="n">
-        <v>34.95</v>
+        <v>23.66</v>
       </c>
       <c r="O309" t="n">
-        <v>15.19</v>
+        <v>10.03</v>
       </c>
       <c r="P309" t="n">
-        <v>482.797</v>
+        <v>322.2</v>
       </c>
       <c r="Q309" t="n">
-        <v>31.78387096774194</v>
+        <v>32.12362911266202</v>
       </c>
       <c r="R309" t="n">
-        <v>434.620886981402</v>
+        <v>423.9222316145393</v>
       </c>
       <c r="S309" t="n">
-        <v>0.5846666666666667</v>
+        <v>0.5976666666666667</v>
       </c>
       <c r="T309" t="n">
         <v>0.585</v>
@@ -29253,37 +29449,37 @@
       </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" t="n">
-        <v>1.645927369808684</v>
+        <v>2.083603463311396</v>
       </c>
       <c r="X309" t="n">
-        <v>520.02068</v>
+        <v>523.43105</v>
       </c>
       <c r="Y309" t="n">
-        <v>15.24436</v>
+        <v>12.98718</v>
       </c>
       <c r="Z309" t="n">
-        <v>1.060681081061475</v>
+        <v>0.7321314863248521</v>
       </c>
       <c r="AA309" t="n">
-        <v>0.0325619423628069</v>
+        <v>0.1893607037452722</v>
       </c>
       <c r="AB309" t="n">
-        <v>2.891816589846828</v>
+        <v>2.871167133566332</v>
       </c>
       <c r="AC309" t="n">
-        <v>0.02768839215525221</v>
+        <v>0.02958686485414572</v>
       </c>
       <c r="AD309" t="n">
-        <v>5.334707698656458</v>
+        <v>5.063811455891623</v>
       </c>
       <c r="AE309" t="n">
-        <v>2.029258417161623</v>
+        <v>1.358562612470712</v>
       </c>
       <c r="AF309" t="n">
-        <v>0.03049873209915185</v>
+        <v>0.007997349112784484</v>
       </c>
       <c r="AG309" t="n">
-        <v>0.7125169065607428</v>
+        <v>0.5494517131458277</v>
       </c>
       <c r="AH309" t="inlineStr"/>
       <c r="AI309" t="inlineStr"/>
@@ -29318,7 +29514,7 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>6994</v>
+        <v>335</v>
       </c>
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
@@ -29338,22 +29534,22 @@
         <v>20</v>
       </c>
       <c r="N310" t="n">
-        <v>25.42</v>
+        <v>41.24</v>
       </c>
       <c r="O310" t="n">
-        <v>9.960000000000001</v>
+        <v>17.46</v>
       </c>
       <c r="P310" t="n">
-        <v>414.662</v>
+        <v>682.298</v>
       </c>
       <c r="Q310" t="n">
-        <v>41.63273092369477</v>
+        <v>39.07777777777778</v>
       </c>
       <c r="R310" t="n">
-        <v>391.8174665617624</v>
+        <v>423.3753637245393</v>
       </c>
       <c r="S310" t="n">
-        <v>0.5203333333333333</v>
+        <v>0.4503333333333333</v>
       </c>
       <c r="T310" t="n">
         <v>0.585</v>
@@ -29363,37 +29559,37 @@
       </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" t="n">
-        <v>1.627624551353116</v>
+        <v>1.609586991136035</v>
       </c>
       <c r="X310" t="n">
-        <v>517.31335</v>
+        <v>518.22426</v>
       </c>
       <c r="Y310" t="n">
-        <v>14.5382</v>
+        <v>13.55855</v>
       </c>
       <c r="Z310" t="n">
-        <v>0.876007634737751</v>
+        <v>0.7135182431806696</v>
       </c>
       <c r="AA310" t="n">
-        <v>0.08882237222577244</v>
+        <v>0.006828840751603856</v>
       </c>
       <c r="AB310" t="n">
-        <v>4.826290506065171</v>
+        <v>2.96597322453885</v>
       </c>
       <c r="AC310" t="n">
-        <v>0.04264856647420304</v>
+        <v>0.01619252395857507</v>
       </c>
       <c r="AD310" t="n">
-        <v>5.52778822181687</v>
+        <v>5.344206441758873</v>
       </c>
       <c r="AE310" t="n">
-        <v>3.169718443828744</v>
+        <v>1.541547902825075</v>
       </c>
       <c r="AF310" t="n">
-        <v>0</v>
+        <v>0.08473257265524321</v>
       </c>
       <c r="AG310" t="n">
-        <v>0.7328988444232435</v>
+        <v>0.6074550655988233</v>
       </c>
       <c r="AH310" t="inlineStr"/>
       <c r="AI310" t="inlineStr"/>
@@ -29428,7 +29624,7 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
@@ -29439,7 +29635,7 @@
         </is>
       </c>
       <c r="K311" s="2" t="n">
-        <v>45266</v>
+        <v>45268</v>
       </c>
       <c r="L311" t="n">
         <v>2000</v>
@@ -29448,22 +29644,22 @@
         <v>20</v>
       </c>
       <c r="N311" t="n">
-        <v>23.66</v>
+        <v>67.78</v>
       </c>
       <c r="O311" t="n">
-        <v>10.03</v>
+        <v>27.64</v>
       </c>
       <c r="P311" t="n">
-        <v>322.2</v>
+        <v>1152.207</v>
       </c>
       <c r="Q311" t="n">
-        <v>32.12362911266202</v>
+        <v>41.68621562952244</v>
       </c>
       <c r="R311" t="n">
-        <v>423.9222316145393</v>
+        <v>407.7899085275893</v>
       </c>
       <c r="S311" t="n">
-        <v>0.5976666666666667</v>
+        <v>0.4989999999999999</v>
       </c>
       <c r="T311" t="n">
         <v>0.585</v>
@@ -29473,37 +29669,37 @@
       </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" t="n">
-        <v>2.083603463311396</v>
+        <v>1.665556479456685</v>
       </c>
       <c r="X311" t="n">
-        <v>523.43105</v>
+        <v>512.37827</v>
       </c>
       <c r="Y311" t="n">
-        <v>12.98718</v>
+        <v>14.31949</v>
       </c>
       <c r="Z311" t="n">
-        <v>0.7321314863248521</v>
+        <v>0.7889988860287893</v>
       </c>
       <c r="AA311" t="n">
-        <v>0.1893607037452722</v>
+        <v>0.3368908464417669</v>
       </c>
       <c r="AB311" t="n">
-        <v>2.871167133566332</v>
+        <v>4.570274845803839</v>
       </c>
       <c r="AC311" t="n">
-        <v>0.02958686485414572</v>
+        <v>0.04353929818648612</v>
       </c>
       <c r="AD311" t="n">
-        <v>5.063811455891623</v>
+        <v>5.062560220754294</v>
       </c>
       <c r="AE311" t="n">
-        <v>1.358562612470712</v>
+        <v>2.63326178702708</v>
       </c>
       <c r="AF311" t="n">
-        <v>0.007997349112784484</v>
+        <v>0.01646630650916846</v>
       </c>
       <c r="AG311" t="n">
-        <v>0.5494517131458277</v>
+        <v>0.521466838872097</v>
       </c>
       <c r="AH311" t="inlineStr"/>
       <c r="AI311" t="inlineStr"/>
@@ -29526,11 +29722,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>SFNu_7</t>
+          <t>SFNu_1</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -29538,7 +29734,7 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>335</v>
+        <v>9091</v>
       </c>
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
@@ -29549,7 +29745,7 @@
         </is>
       </c>
       <c r="K312" s="2" t="n">
-        <v>45275</v>
+        <v>45266</v>
       </c>
       <c r="L312" t="n">
         <v>2000</v>
@@ -29558,22 +29754,22 @@
         <v>20</v>
       </c>
       <c r="N312" t="n">
-        <v>41.24</v>
+        <v>34.25</v>
       </c>
       <c r="O312" t="n">
-        <v>17.46</v>
+        <v>14.43</v>
       </c>
       <c r="P312" t="n">
-        <v>682.298</v>
+        <v>566.856</v>
       </c>
       <c r="Q312" t="n">
-        <v>39.07777777777778</v>
+        <v>39.28316008316008</v>
       </c>
       <c r="R312" t="n">
-        <v>423.3753637245393</v>
+        <v>421.3138686131387</v>
       </c>
       <c r="S312" t="n">
-        <v>0.4503333333333333</v>
+        <v>0.469</v>
       </c>
       <c r="T312" t="n">
         <v>0.585</v>
@@ -29583,261 +29779,41 @@
       </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" t="n">
-        <v>1.609586991136035</v>
+        <v>1.635317040269225</v>
       </c>
       <c r="X312" t="n">
-        <v>518.22426</v>
+        <v>526.9802500000001</v>
       </c>
       <c r="Y312" t="n">
-        <v>13.55855</v>
+        <v>14.71585</v>
       </c>
       <c r="Z312" t="n">
-        <v>0.7135182431806696</v>
+        <v>0.8868190945788528</v>
       </c>
       <c r="AA312" t="n">
-        <v>0.006828840751603856</v>
+        <v>0.1486261449063734</v>
       </c>
       <c r="AB312" t="n">
-        <v>2.96597322453885</v>
+        <v>2.847093168686002</v>
       </c>
       <c r="AC312" t="n">
-        <v>0.01619252395857507</v>
+        <v>0.02883335817085085</v>
       </c>
       <c r="AD312" t="n">
-        <v>5.344206441758873</v>
+        <v>4.683287747999575</v>
       </c>
       <c r="AE312" t="n">
-        <v>1.541547902825075</v>
+        <v>1.949722974162664</v>
       </c>
       <c r="AF312" t="n">
-        <v>0.08473257265524321</v>
+        <v>0</v>
       </c>
       <c r="AG312" t="n">
-        <v>0.6074550655988233</v>
+        <v>0.3099619162837322</v>
       </c>
       <c r="AH312" t="inlineStr"/>
       <c r="AI312" t="inlineStr"/>
       <c r="AJ312" t="inlineStr">
-        <is>
-          <t>data_for_R.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>SFNu</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>SFNu_1</t>
-        </is>
-      </c>
-      <c r="D313" t="n">
-        <v>1</v>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F313" t="n">
-        <v>101</v>
-      </c>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>Alchornea lojaensis</t>
-        </is>
-      </c>
-      <c r="K313" s="2" t="n">
-        <v>45268</v>
-      </c>
-      <c r="L313" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M313" t="n">
-        <v>20</v>
-      </c>
-      <c r="N313" t="n">
-        <v>67.78</v>
-      </c>
-      <c r="O313" t="n">
-        <v>27.64</v>
-      </c>
-      <c r="P313" t="n">
-        <v>1152.207</v>
-      </c>
-      <c r="Q313" t="n">
-        <v>41.68621562952244</v>
-      </c>
-      <c r="R313" t="n">
-        <v>407.7899085275893</v>
-      </c>
-      <c r="S313" t="n">
-        <v>0.4989999999999999</v>
-      </c>
-      <c r="T313" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="U313" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="V313" t="inlineStr"/>
-      <c r="W313" t="n">
-        <v>1.665556479456685</v>
-      </c>
-      <c r="X313" t="n">
-        <v>512.37827</v>
-      </c>
-      <c r="Y313" t="n">
-        <v>14.31949</v>
-      </c>
-      <c r="Z313" t="n">
-        <v>0.7889988860287893</v>
-      </c>
-      <c r="AA313" t="n">
-        <v>0.3368908464417669</v>
-      </c>
-      <c r="AB313" t="n">
-        <v>4.570274845803839</v>
-      </c>
-      <c r="AC313" t="n">
-        <v>0.04353929818648612</v>
-      </c>
-      <c r="AD313" t="n">
-        <v>5.062560220754294</v>
-      </c>
-      <c r="AE313" t="n">
-        <v>2.63326178702708</v>
-      </c>
-      <c r="AF313" t="n">
-        <v>0.01646630650916846</v>
-      </c>
-      <c r="AG313" t="n">
-        <v>0.521466838872097</v>
-      </c>
-      <c r="AH313" t="inlineStr"/>
-      <c r="AI313" t="inlineStr"/>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>data_for_R.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>SFNu</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>SFNu_1</t>
-        </is>
-      </c>
-      <c r="D314" t="n">
-        <v>1</v>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F314" t="n">
-        <v>9091</v>
-      </c>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>Alchornea lojaensis</t>
-        </is>
-      </c>
-      <c r="K314" s="2" t="n">
-        <v>45266</v>
-      </c>
-      <c r="L314" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M314" t="n">
-        <v>20</v>
-      </c>
-      <c r="N314" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="O314" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="P314" t="n">
-        <v>566.856</v>
-      </c>
-      <c r="Q314" t="n">
-        <v>39.28316008316008</v>
-      </c>
-      <c r="R314" t="n">
-        <v>421.3138686131387</v>
-      </c>
-      <c r="S314" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="T314" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="U314" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="V314" t="inlineStr"/>
-      <c r="W314" t="n">
-        <v>1.635317040269225</v>
-      </c>
-      <c r="X314" t="n">
-        <v>526.9802500000001</v>
-      </c>
-      <c r="Y314" t="n">
-        <v>14.71585</v>
-      </c>
-      <c r="Z314" t="n">
-        <v>0.8868190945788528</v>
-      </c>
-      <c r="AA314" t="n">
-        <v>0.1486261449063734</v>
-      </c>
-      <c r="AB314" t="n">
-        <v>2.847093168686002</v>
-      </c>
-      <c r="AC314" t="n">
-        <v>0.02883335817085085</v>
-      </c>
-      <c r="AD314" t="n">
-        <v>4.683287747999575</v>
-      </c>
-      <c r="AE314" t="n">
-        <v>1.949722974162664</v>
-      </c>
-      <c r="AF314" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG314" t="n">
-        <v>0.3099619162837322</v>
-      </c>
-      <c r="AH314" t="inlineStr"/>
-      <c r="AI314" t="inlineStr"/>
-      <c r="AJ314" t="inlineStr">
         <is>
           <t>data_for_R.xlsx</t>
         </is>
